--- a/晚高峰客流量调查数据1.xlsx
+++ b/晚高峰客流量调查数据1.xlsx
@@ -5,16 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\word\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\公共交通课程设计\ggjt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E1739B-7DED-46E3-B560-552D8B280762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755F7DD5-00EE-4402-96B1-82EA2573EBD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="73">
   <si>
     <t>公交线路客流调查表</t>
   </si>
@@ -106,9 +110,6 @@
   </si>
   <si>
     <t xml:space="preserve">   东体育馆</t>
-  </si>
-  <si>
-    <t>总结</t>
   </si>
   <si>
     <t>总计</t>
@@ -238,6 +239,33 @@
     <t>（1-15的客运量）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>下车人数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>总计</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>调查线路：某路</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>发车间隔：1分钟</t>
+  </si>
+  <si>
+    <t>发车时间：18.03</t>
+  </si>
+  <si>
+    <t>到达时间：18.44</t>
+  </si>
+  <si>
+    <t>发车时间：18.04</t>
+  </si>
+  <si>
+    <t>到达时间：18.45</t>
+  </si>
 </sst>
 </file>
 
@@ -262,6 +290,7 @@
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -287,15 +316,39 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59996337778862885"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -318,13 +371,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -364,13 +454,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -592,6 +712,12 @@
       <tableStyleElement type="pageFieldValues" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="FF5D5365"/>
+      <color rgb="FF6600FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -7322,6 +7448,209 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="67">
+          <cell r="B67" t="str">
+            <v>途径站点</v>
+          </cell>
+          <cell r="C67" t="str">
+            <v>上车人数</v>
+          </cell>
+          <cell r="D67" t="str">
+            <v>下车人数</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="B68" t="str">
+            <v>东体育馆</v>
+          </cell>
+          <cell r="C68">
+            <v>4</v>
+          </cell>
+          <cell r="D68">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="B69" t="str">
+            <v>融园东</v>
+          </cell>
+          <cell r="C69">
+            <v>17</v>
+          </cell>
+          <cell r="D69">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="B70" t="str">
+            <v>第三食堂</v>
+          </cell>
+          <cell r="C70">
+            <v>5</v>
+          </cell>
+          <cell r="D70">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="B71" t="str">
+            <v>秀园</v>
+          </cell>
+          <cell r="C71">
+            <v>1</v>
+          </cell>
+          <cell r="D71">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="B72" t="str">
+            <v>第二食堂</v>
+          </cell>
+          <cell r="C72">
+            <v>4</v>
+          </cell>
+          <cell r="D72">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="B73" t="str">
+            <v>综合楼</v>
+          </cell>
+          <cell r="C73">
+            <v>0</v>
+          </cell>
+          <cell r="D73">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="B74" t="str">
+            <v>一食堂</v>
+          </cell>
+          <cell r="C74">
+            <v>2</v>
+          </cell>
+          <cell r="D74">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="B75" t="str">
+            <v>西门</v>
+          </cell>
+          <cell r="C75">
+            <v>2</v>
+          </cell>
+          <cell r="D75">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="B76" t="str">
+            <v>纺化楼</v>
+          </cell>
+          <cell r="C76">
+            <v>0</v>
+          </cell>
+          <cell r="D76">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="B77" t="str">
+            <v>11号教学楼</v>
+          </cell>
+          <cell r="C77">
+            <v>3</v>
+          </cell>
+          <cell r="D77">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="B78" t="str">
+            <v>1号教学楼</v>
+          </cell>
+          <cell r="C78">
+            <v>4</v>
+          </cell>
+          <cell r="D78">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="B79" t="str">
+            <v>逸夫楼</v>
+          </cell>
+          <cell r="C79">
+            <v>1</v>
+          </cell>
+          <cell r="D79">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="B80" t="str">
+            <v>理科楼</v>
+          </cell>
+          <cell r="C80">
+            <v>0</v>
+          </cell>
+          <cell r="D80">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="B81" t="str">
+            <v>东操场</v>
+          </cell>
+          <cell r="C81">
+            <v>0</v>
+          </cell>
+          <cell r="D81">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="B82" t="str">
+            <v>东体育馆</v>
+          </cell>
+          <cell r="C82">
+            <v>0</v>
+          </cell>
+          <cell r="D82">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="C83">
+            <v>43</v>
+          </cell>
+          <cell r="D83">
+            <v>43</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -7581,73 +7910,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N234"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="29.1796875" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" customWidth="1"/>
-    <col min="3" max="3" width="18.1796875" customWidth="1"/>
+    <col min="1" max="1" width="29.125" customWidth="1"/>
+    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="23.81640625" customWidth="1"/>
-    <col min="6" max="6" width="29.1796875" customWidth="1"/>
-    <col min="7" max="7" width="16.08984375" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" customWidth="1"/>
-    <col min="9" max="9" width="17.1796875" customWidth="1"/>
-    <col min="10" max="10" width="11.6328125" customWidth="1"/>
-    <col min="11" max="11" width="9.54296875" customWidth="1"/>
+    <col min="5" max="5" width="23.875" customWidth="1"/>
+    <col min="6" max="6" width="29.125" customWidth="1"/>
+    <col min="7" max="7" width="16.125" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="17.125" customWidth="1"/>
+    <col min="10" max="10" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -7663,8 +7992,8 @@
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
+      <c r="F4" s="12" t="s">
+        <v>65</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>4</v>
@@ -7682,7 +8011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -7717,7 +8046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -7752,7 +8081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -7787,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>4</v>
       </c>
@@ -7822,7 +8151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>5</v>
       </c>
@@ -7857,7 +8186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>6</v>
       </c>
@@ -7892,7 +8221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>7</v>
       </c>
@@ -7927,7 +8256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>8</v>
       </c>
@@ -7962,7 +8291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>9</v>
       </c>
@@ -7997,7 +8326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10</v>
       </c>
@@ -8032,7 +8361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>11</v>
       </c>
@@ -8067,7 +8396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>12</v>
       </c>
@@ -8102,7 +8431,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>13</v>
       </c>
@@ -8137,7 +8466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>14</v>
       </c>
@@ -8172,7 +8501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>15</v>
       </c>
@@ -8207,9 +8536,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A20" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -8234,7 +8563,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -8247,7 +8576,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -8262,7 +8591,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
@@ -8279,15 +8608,15 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A24" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="12" t="s">
         <v>59</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>60</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -8298,7 +8627,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
         <v>3</v>
       </c>
@@ -8333,7 +8662,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>1</v>
       </c>
@@ -8370,7 +8699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>2</v>
       </c>
@@ -8407,7 +8736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -8415,7 +8744,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" ref="C27:C40" si="1">C7+0.01</f>
+        <f t="shared" ref="C28:C40" si="1">C7+0.01</f>
         <v>18.07</v>
       </c>
       <c r="D28" s="3">
@@ -8444,7 +8773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -8481,7 +8810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>5</v>
       </c>
@@ -8518,7 +8847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>6</v>
       </c>
@@ -8555,7 +8884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>7</v>
       </c>
@@ -8592,7 +8921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>8</v>
       </c>
@@ -8629,7 +8958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>9</v>
       </c>
@@ -8666,7 +8995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>10</v>
       </c>
@@ -8703,7 +9032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>11</v>
       </c>
@@ -8740,7 +9069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>12</v>
       </c>
@@ -8777,7 +9106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>13</v>
       </c>
@@ -8813,7 +9142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>14</v>
       </c>
@@ -8850,7 +9179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>15</v>
       </c>
@@ -8887,9 +9216,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -8914,7 +9243,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -8927,7 +9256,7 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -8942,7 +9271,7 @@
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
         <v>1</v>
       </c>
@@ -8959,15 +9288,15 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A45" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B45" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="C45" s="12" t="s">
         <v>62</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>63</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -8978,7 +9307,7 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
@@ -9013,7 +9342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -9050,7 +9379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>2</v>
       </c>
@@ -9087,7 +9416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>3</v>
       </c>
@@ -9123,7 +9452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>4</v>
       </c>
@@ -9160,7 +9489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9196,7 +9525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>6</v>
       </c>
@@ -9233,7 +9562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>7</v>
       </c>
@@ -9270,7 +9599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>8</v>
       </c>
@@ -9306,7 +9635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>9</v>
       </c>
@@ -9343,7 +9672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>10</v>
       </c>
@@ -9380,7 +9709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>11</v>
       </c>
@@ -9416,7 +9745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>12</v>
       </c>
@@ -9452,12 +9781,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>13</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C59" s="3">
         <f t="shared" si="2"/>
@@ -9488,7 +9817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>14</v>
       </c>
@@ -9524,7 +9853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>15</v>
       </c>
@@ -9561,9 +9890,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -9588,7 +9917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -9601,621 +9930,621 @@
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A64" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="20"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B65" s="1" t="s">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A65" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B65" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G65" s="1" t="s">
+      <c r="F65" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A66" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D66" s="1"/>
+      <c r="D66" s="15"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G66" s="1" t="s">
+      <c r="F66" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H66" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I66" s="1"/>
+      <c r="I66" s="15"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A67" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="15" t="s">
         <v>8</v>
       </c>
       <c r="E67" s="1"/>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" s="15" t="s">
         <v>8</v>
       </c>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
-        <v>1</v>
-      </c>
-      <c r="B68" s="2" t="s">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A68" s="15">
+        <v>1</v>
+      </c>
+      <c r="B68" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="15">
         <f t="shared" ref="C68:D73" si="3">E5+E26+E47</f>
         <v>7</v>
       </c>
-      <c r="D68" s="1">
+      <c r="D68" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E68" s="1"/>
-      <c r="F68" s="1">
-        <v>1</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="F68" s="15">
+        <v>1</v>
+      </c>
+      <c r="G68" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H68" s="1">
+      <c r="H68" s="15">
         <f>J5+J26+J47</f>
         <v>7</v>
       </c>
-      <c r="I68" s="1">
+      <c r="I68" s="15">
         <f>K5+K26+K47</f>
         <v>0</v>
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A69" s="15">
         <v>2</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="15">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
-      <c r="D69" s="1">
+      <c r="D69" s="15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E69" s="1"/>
-      <c r="F69" s="1">
+      <c r="F69" s="15">
         <v>2</v>
       </c>
-      <c r="G69" s="2" t="s">
+      <c r="G69" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="H69" s="1">
+      <c r="H69" s="15">
         <f t="shared" ref="H69:H82" si="4">J6+J27+J48</f>
         <v>0</v>
       </c>
-      <c r="I69" s="1">
+      <c r="I69" s="15">
         <f t="shared" ref="I69:I82" si="5">K6+K27+K48</f>
         <v>3</v>
       </c>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A70" s="15">
         <v>3</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="D70" s="1">
+      <c r="D70" s="15">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="E70" s="1"/>
-      <c r="F70" s="1">
+      <c r="F70" s="15">
         <v>3</v>
       </c>
-      <c r="G70" s="2" t="s">
+      <c r="G70" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="H70" s="1">
+      <c r="H70" s="15">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="I70" s="1">
+      <c r="I70" s="15">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A71" s="15">
         <v>4</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C71" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="D71" s="1">
+      <c r="D71" s="15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E71" s="1"/>
-      <c r="F71" s="1">
+      <c r="F71" s="15">
         <v>4</v>
       </c>
-      <c r="G71" s="2" t="s">
+      <c r="G71" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H71" s="1">
+      <c r="H71" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="I71" s="1">
+      <c r="I71" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A72" s="15">
         <v>5</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72" s="15">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72" s="15">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="E72" s="1"/>
-      <c r="F72" s="1">
+      <c r="F72" s="15">
         <v>5</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G72" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="H72" s="1">
+      <c r="H72" s="15">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="I72" s="1">
+      <c r="I72" s="15">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A73" s="15">
         <v>6</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C73" s="1">
+      <c r="C73" s="15">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="D73" s="1">
+      <c r="D73" s="15">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E73" s="1"/>
-      <c r="F73" s="1">
+      <c r="F73" s="15">
         <v>6</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="G73" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="H73" s="1">
+      <c r="H73" s="15">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="I73" s="1">
+      <c r="I73" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A74" s="15">
         <v>7</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C74" s="1">
+      <c r="C74" s="15">
         <f t="shared" ref="C74:C82" si="6">E11+E32+E53</f>
         <v>1</v>
       </c>
-      <c r="D74" s="1">
+      <c r="D74" s="15">
         <f t="shared" ref="D74:D82" si="7">F11+F32+F53</f>
         <v>2</v>
       </c>
       <c r="E74" s="1"/>
-      <c r="F74" s="1">
+      <c r="F74" s="15">
         <v>7</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H74" s="1">
+      <c r="H74" s="15">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="I74" s="1">
+      <c r="I74" s="15">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A75" s="15">
         <v>8</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C75" s="1">
+      <c r="C75" s="15">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D75" s="15">
         <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="E75" s="1"/>
-      <c r="F75" s="1">
+      <c r="F75" s="15">
         <v>8</v>
       </c>
-      <c r="G75" s="2" t="s">
+      <c r="G75" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="H75" s="1">
+      <c r="H75" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I75" s="1">
+      <c r="I75" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A76" s="15">
         <v>9</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C76" s="1">
+      <c r="C76" s="15">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D76" s="15">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E76" s="1"/>
-      <c r="F76" s="1">
+      <c r="F76" s="15">
         <v>9</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H76" s="15">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="I76" s="1">
+      <c r="I76" s="15">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A77" s="15">
         <v>10</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C77" s="1">
+      <c r="C77" s="15">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D77" s="15">
         <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="E77" s="1"/>
-      <c r="F77" s="1">
+      <c r="F77" s="15">
         <v>10</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="G77" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="H77" s="1">
+      <c r="H77" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="I77" s="1">
+      <c r="I77" s="15">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A78" s="15">
         <v>11</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C78" s="1">
+      <c r="C78" s="15">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
-      <c r="D78" s="1">
+      <c r="D78" s="15">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E78" s="1"/>
-      <c r="F78" s="1">
+      <c r="F78" s="15">
         <v>11</v>
       </c>
-      <c r="G78" s="2" t="s">
+      <c r="G78" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="H78" s="1">
+      <c r="H78" s="15">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="I78" s="1">
+      <c r="I78" s="15">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A79" s="15">
         <v>12</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="1">
+      <c r="C79" s="15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="D79" s="1">
+      <c r="D79" s="15">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="E79" s="1"/>
-      <c r="F79" s="1">
+      <c r="F79" s="15">
         <v>12</v>
       </c>
-      <c r="G79" s="2" t="s">
+      <c r="G79" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="H79" s="1">
+      <c r="H79" s="15">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="I79" s="1">
+      <c r="I79" s="15">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A80" s="15">
         <v>13</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C80" s="1">
+      <c r="C80" s="15">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="D80" s="1">
+      <c r="D80" s="15">
         <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="E80" s="1"/>
-      <c r="F80" s="1">
+      <c r="F80" s="15">
         <v>13</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="G80" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H80" s="1">
+      <c r="H80" s="15">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="I80" s="1">
+      <c r="I80" s="15">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A81" s="15">
         <v>14</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C81" s="1">
+      <c r="C81" s="15">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
-      <c r="D81" s="1">
+      <c r="D81" s="15">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E81" s="1"/>
-      <c r="F81" s="1">
+      <c r="F81" s="15">
         <v>14</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="G81" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="H81" s="1">
+      <c r="H81" s="15">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="I81" s="1">
+      <c r="I81" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A82" s="15">
         <v>15</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82" s="15">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82" s="15">
         <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="E82" s="1"/>
-      <c r="F82" s="1">
+      <c r="F82" s="15">
         <v>15</v>
       </c>
-      <c r="G82" s="2" t="s">
+      <c r="G82" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="H82" s="1">
+      <c r="H82" s="15">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I82" s="1">
+      <c r="I82" s="15">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A83" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" s="15"/>
+      <c r="C83" s="15">
         <f>SUM(C68:C82)</f>
         <v>56</v>
       </c>
-      <c r="D83" s="1">
+      <c r="D83" s="15">
         <f>SUM(D68:D82)</f>
         <v>56</v>
       </c>
       <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1">
+      <c r="F83" s="15"/>
+      <c r="G83" s="15"/>
+      <c r="H83" s="15">
         <f>SUM(H68:H82)</f>
         <v>54</v>
       </c>
-      <c r="I83" s="1">
+      <c r="I83" s="15">
         <f>SUM(I68:I82)</f>
         <v>54</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -10228,7 +10557,7 @@
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -10241,7 +10570,7 @@
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -10254,7 +10583,7 @@
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -10267,7 +10596,7 @@
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -10280,7 +10609,7 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -10293,7 +10622,7 @@
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -10306,7 +10635,7 @@
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -10319,7 +10648,7 @@
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -10332,7 +10661,7 @@
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -10345,7 +10674,7 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -10358,7 +10687,7 @@
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -10371,7 +10700,7 @@
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -10384,7 +10713,7 @@
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -10397,7 +10726,7 @@
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -10410,7 +10739,7 @@
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -10423,7 +10752,7 @@
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -10436,7 +10765,7 @@
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -10449,7 +10778,7 @@
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -10462,7 +10791,7 @@
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -10475,7 +10804,7 @@
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -10488,7 +10817,7 @@
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -10501,20 +10830,20 @@
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A106" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" s="24" t="s">
         <v>36</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
-      <c r="E106" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F106" s="1" t="s">
+      <c r="E106" s="24" t="s">
         <v>37</v>
+      </c>
+      <c r="F106" s="24" t="s">
+        <v>36</v>
       </c>
       <c r="G106" s="1"/>
       <c r="H106" s="1"/>
@@ -10522,20 +10851,20 @@
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A107" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B107" s="1">
+      <c r="B107" s="24">
         <f>C68-D68</f>
         <v>7</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
-      <c r="E107" s="2" t="s">
+      <c r="E107" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F107" s="1">
+      <c r="F107" s="24">
         <f>H68-I68</f>
         <v>7</v>
       </c>
@@ -10545,20 +10874,20 @@
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="2" t="s">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A108" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B108" s="1">
+      <c r="B108" s="24">
         <f>B107+C69-D69</f>
         <v>19</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
-      <c r="E108" s="2" t="s">
+      <c r="E108" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="F108" s="1">
+      <c r="F108" s="24">
         <f>F107+H69-I69</f>
         <v>4</v>
       </c>
@@ -10568,20 +10897,20 @@
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="2" t="s">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A109" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="B109" s="1">
+      <c r="B109" s="24">
         <f t="shared" ref="B109:B121" si="8">B108+C70-D70</f>
         <v>11</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
-      <c r="E109" s="2" t="s">
+      <c r="E109" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="1">
+      <c r="F109" s="24">
         <f t="shared" ref="F109:F121" si="9">F108+H70-I70</f>
         <v>9</v>
       </c>
@@ -10591,20 +10920,20 @@
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="2" t="s">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A110" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B110" s="1">
+      <c r="B110" s="24">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
-      <c r="E110" s="2" t="s">
+      <c r="E110" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="F110" s="1">
+      <c r="F110" s="24">
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
@@ -10614,20 +10943,20 @@
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="2" t="s">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A111" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B111" s="1">
+      <c r="B111" s="24">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
-      <c r="E111" s="2" t="s">
+      <c r="E111" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="F111" s="1">
+      <c r="F111" s="24">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
@@ -10637,20 +10966,20 @@
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="2" t="s">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A112" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="B112" s="1">
+      <c r="B112" s="24">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
-      <c r="E112" s="2" t="s">
+      <c r="E112" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F112" s="1">
+      <c r="F112" s="24">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
@@ -10660,20 +10989,20 @@
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="2" t="s">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A113" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B113" s="1">
+      <c r="B113" s="24">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
-      <c r="E113" s="2" t="s">
+      <c r="E113" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="F113" s="1">
+      <c r="F113" s="24">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
@@ -10683,20 +11012,20 @@
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="2" t="s">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A114" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="B114" s="1">
+      <c r="B114" s="24">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
-      <c r="E114" s="2" t="s">
+      <c r="E114" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="F114" s="1">
+      <c r="F114" s="24">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
@@ -10706,20 +11035,20 @@
       <c r="J114" s="1"/>
       <c r="K114" s="1"/>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="2" t="s">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A115" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B115" s="1">
+      <c r="B115" s="24">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
-      <c r="E115" s="2" t="s">
+      <c r="E115" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F115" s="1">
+      <c r="F115" s="24">
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
@@ -10729,20 +11058,20 @@
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A116" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="B116" s="1">
+      <c r="B116" s="24">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
-      <c r="E116" s="2" t="s">
+      <c r="E116" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F116" s="1">
+      <c r="F116" s="24">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
@@ -10752,20 +11081,20 @@
       <c r="J116" s="1"/>
       <c r="K116" s="1"/>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A117" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B117" s="1">
+      <c r="B117" s="24">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
-      <c r="E117" s="2" t="s">
+      <c r="E117" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="F117" s="1">
+      <c r="F117" s="24">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
@@ -10775,20 +11104,20 @@
       <c r="J117" s="1"/>
       <c r="K117" s="1"/>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A118" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B118" s="1">
+      <c r="B118" s="24">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
-      <c r="E118" s="2" t="s">
+      <c r="E118" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="F118" s="1">
+      <c r="F118" s="24">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -10798,20 +11127,20 @@
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A119" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B119" s="1">
+      <c r="B119" s="24">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
-      <c r="E119" s="2" t="s">
+      <c r="E119" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="F119" s="1">
+      <c r="F119" s="24">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -10821,20 +11150,20 @@
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A120" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B120" s="1">
+      <c r="B120" s="24">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
-      <c r="E120" s="2" t="s">
+      <c r="E120" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F120" s="1">
+      <c r="F120" s="24">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -10844,20 +11173,20 @@
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A121" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="B121" s="1">
+      <c r="B121" s="24">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
-      <c r="E121" s="2" t="s">
+      <c r="E121" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F121" s="1">
+      <c r="F121" s="24">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -10867,7 +11196,7 @@
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A122" s="5"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -10880,7 +11209,7 @@
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A123" s="5"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -10893,7 +11222,7 @@
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A124" s="5"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -10906,9 +11235,9 @@
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
     </row>
-    <row r="125" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>7</v>
@@ -10929,19 +11258,19 @@
         <v>8</v>
       </c>
       <c r="H125" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I125" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="I125" s="6" t="s">
+      <c r="J125" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J125" s="6" t="s">
+      <c r="K125" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K125" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
         <v>9</v>
       </c>
@@ -10980,7 +11309,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
         <v>10</v>
       </c>
@@ -11019,7 +11348,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
         <v>12</v>
       </c>
@@ -11058,7 +11387,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
         <v>14</v>
       </c>
@@ -11097,7 +11426,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
         <v>16</v>
       </c>
@@ -11136,7 +11465,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
         <v>18</v>
       </c>
@@ -11175,7 +11504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
         <v>20</v>
       </c>
@@ -11214,7 +11543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
         <v>22</v>
       </c>
@@ -11253,7 +11582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
         <v>21</v>
       </c>
@@ -11292,7 +11621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
         <v>19</v>
       </c>
@@ -11331,7 +11660,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
         <v>17</v>
       </c>
@@ -11370,7 +11699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
         <v>15</v>
       </c>
@@ -11409,7 +11738,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
         <v>13</v>
       </c>
@@ -11448,7 +11777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
         <v>11</v>
       </c>
@@ -11487,7 +11816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
         <v>9</v>
       </c>
@@ -11526,7 +11855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A141" s="1"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
@@ -11539,7 +11868,7 @@
       <c r="J141" s="10"/>
       <c r="K141" s="9"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A142" s="1"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
@@ -11552,7 +11881,7 @@
       <c r="J142" s="10"/>
       <c r="K142" s="9"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A143" s="1"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
@@ -11565,9 +11894,9 @@
       <c r="J143" s="10"/>
       <c r="K143" s="9"/>
     </row>
-    <row r="144" spans="1:11" ht="27" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>7</v>
@@ -11588,19 +11917,19 @@
         <v>8</v>
       </c>
       <c r="H144" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I144" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I144" s="7" t="s">
+      <c r="J144" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J144" s="7" t="s">
+      <c r="K144" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="K144" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
         <v>9</v>
       </c>
@@ -11634,12 +11963,12 @@
         <f>H145-I145</f>
         <v>2.3333333333333335</v>
       </c>
-      <c r="K145" s="15">
+      <c r="K145" s="13">
         <f>F107</f>
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
         <v>11</v>
       </c>
@@ -11673,12 +12002,12 @@
         <f>J145+H146-I146</f>
         <v>1.3333333333333335</v>
       </c>
-      <c r="K146" s="15">
+      <c r="K146" s="13">
         <f t="shared" ref="K146:K159" si="16">F108</f>
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
         <v>13</v>
       </c>
@@ -11712,12 +12041,12 @@
         <f t="shared" ref="J147:J159" si="17">J146+H147-I147</f>
         <v>3</v>
       </c>
-      <c r="K147" s="15">
+      <c r="K147" s="13">
         <f t="shared" si="16"/>
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
         <v>15</v>
       </c>
@@ -11751,12 +12080,12 @@
         <f t="shared" si="17"/>
         <v>3</v>
       </c>
-      <c r="K148" s="15">
+      <c r="K148" s="13">
         <f t="shared" si="16"/>
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
         <v>17</v>
       </c>
@@ -11790,12 +12119,12 @@
         <f t="shared" si="17"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="K149" s="15">
+      <c r="K149" s="13">
         <f t="shared" si="16"/>
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
         <v>19</v>
       </c>
@@ -11829,12 +12158,12 @@
         <f t="shared" si="17"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="K150" s="15">
+      <c r="K150" s="13">
         <f t="shared" si="16"/>
         <v>19</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
         <v>21</v>
       </c>
@@ -11868,12 +12197,12 @@
         <f t="shared" si="17"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="K151" s="15">
+      <c r="K151" s="13">
         <f t="shared" si="16"/>
         <v>19</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
         <v>22</v>
       </c>
@@ -11907,12 +12236,12 @@
         <f t="shared" si="17"/>
         <v>5.9999999999999991</v>
       </c>
-      <c r="K152" s="15">
+      <c r="K152" s="13">
         <f t="shared" si="16"/>
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
         <v>20</v>
       </c>
@@ -11946,12 +12275,12 @@
         <f t="shared" si="17"/>
         <v>5</v>
       </c>
-      <c r="K153" s="15">
+      <c r="K153" s="13">
         <f t="shared" si="16"/>
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
         <v>18</v>
       </c>
@@ -11985,12 +12314,12 @@
         <f t="shared" si="17"/>
         <v>4.6666666666666661</v>
       </c>
-      <c r="K154" s="15">
+      <c r="K154" s="13">
         <f t="shared" si="16"/>
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
         <v>16</v>
       </c>
@@ -12024,12 +12353,12 @@
         <f t="shared" si="17"/>
         <v>3.333333333333333</v>
       </c>
-      <c r="K155" s="15">
+      <c r="K155" s="13">
         <f t="shared" si="16"/>
         <v>10</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
         <v>14</v>
       </c>
@@ -12063,12 +12392,12 @@
         <f t="shared" si="17"/>
         <v>1.3333333333333335</v>
       </c>
-      <c r="K156" s="15">
+      <c r="K156" s="13">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
         <v>12</v>
       </c>
@@ -12102,12 +12431,12 @@
         <f t="shared" si="17"/>
         <v>1.3333333333333335</v>
       </c>
-      <c r="K157" s="15">
+      <c r="K157" s="13">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
         <v>10</v>
       </c>
@@ -12141,12 +12470,12 @@
         <f t="shared" si="17"/>
         <v>1.3333333333333337</v>
       </c>
-      <c r="K158" s="15">
+      <c r="K158" s="13">
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
         <v>9</v>
       </c>
@@ -12180,12 +12509,12 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K159" s="15">
+      <c r="K159" s="13">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A160" s="1"/>
       <c r="B160" s="9"/>
       <c r="C160" s="9"/>
@@ -12198,7 +12527,7 @@
       <c r="J160" s="10"/>
       <c r="K160" s="1"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A161" s="1"/>
       <c r="B161" s="9"/>
       <c r="C161" s="9"/>
@@ -12211,7 +12540,7 @@
       <c r="J161" s="10"/>
       <c r="K161" s="9"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A162" s="1"/>
       <c r="B162" s="9"/>
       <c r="C162" s="9"/>
@@ -12224,7 +12553,7 @@
       <c r="J162" s="10"/>
       <c r="K162" s="9"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A163" s="1"/>
       <c r="B163" s="9"/>
       <c r="C163" s="9"/>
@@ -12237,7 +12566,7 @@
       <c r="J163" s="10"/>
       <c r="K163" s="9"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -12250,45 +12579,45 @@
       <c r="J164" s="1"/>
       <c r="K164" s="1"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A165" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B165" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B165" s="1" t="s">
+      <c r="C165" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C165" s="1" t="s">
+      <c r="D165" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="E165" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="F165" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F165" s="1" t="s">
+      <c r="G165" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G165" s="1" t="s">
+      <c r="H165" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="I165" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I165" s="1" t="s">
+      <c r="J165" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K165" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J165" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K165" s="1" t="s">
+      <c r="L165" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L165" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A166" s="1"/>
       <c r="B166" s="1">
         <v>1</v>
@@ -12318,15 +12647,15 @@
         <f>G166-H166</f>
         <v>7</v>
       </c>
-      <c r="J166" s="13">
+      <c r="J166" s="21">
         <f>SUM(F166:F180)</f>
         <v>142</v>
       </c>
-      <c r="K166" s="13">
+      <c r="K166" s="21">
         <f>SUM(N166:N179)</f>
         <v>44.449999999999989</v>
       </c>
-      <c r="L166" s="14">
+      <c r="L166" s="23">
         <f>K166/J166</f>
         <v>0.31302816901408442</v>
       </c>
@@ -12335,7 +12664,7 @@
         <v>1.204</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A167" s="1"/>
       <c r="B167" s="1">
         <v>2</v>
@@ -12365,15 +12694,15 @@
         <f t="shared" ref="I167:I180" si="20">G167-H167</f>
         <v>12</v>
       </c>
-      <c r="J167" s="13"/>
-      <c r="K167" s="13"/>
-      <c r="L167" s="14"/>
+      <c r="J167" s="21"/>
+      <c r="K167" s="21"/>
+      <c r="L167" s="23"/>
       <c r="N167">
         <f t="shared" ref="N167:N180" si="21">F167*D168</f>
         <v>6.5170000000000003</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A168" s="1"/>
       <c r="B168" s="1">
         <v>3</v>
@@ -12403,15 +12732,15 @@
         <f t="shared" si="20"/>
         <v>-8</v>
       </c>
-      <c r="J168" s="13"/>
-      <c r="K168" s="13"/>
-      <c r="L168" s="14"/>
+      <c r="J168" s="21"/>
+      <c r="K168" s="21"/>
+      <c r="L168" s="23"/>
       <c r="N168">
         <f t="shared" si="21"/>
         <v>1.9689999999999999</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A169" s="1"/>
       <c r="B169" s="1">
         <v>4</v>
@@ -12441,15 +12770,15 @@
         <f t="shared" si="20"/>
         <v>-2</v>
       </c>
-      <c r="J169" s="13"/>
-      <c r="K169" s="13"/>
-      <c r="L169" s="14"/>
+      <c r="J169" s="21"/>
+      <c r="K169" s="21"/>
+      <c r="L169" s="23"/>
       <c r="N169">
         <f t="shared" si="21"/>
         <v>2.7359999999999998</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="1"/>
       <c r="B170" s="1">
         <v>5</v>
@@ -12479,15 +12808,15 @@
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="J170" s="13"/>
-      <c r="K170" s="13"/>
-      <c r="L170" s="14"/>
+      <c r="J170" s="21"/>
+      <c r="K170" s="21"/>
+      <c r="L170" s="23"/>
       <c r="N170">
         <f t="shared" si="21"/>
         <v>4.7189999999999994</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A171" s="1"/>
       <c r="B171" s="1">
         <v>6</v>
@@ -12517,15 +12846,15 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="J171" s="13"/>
-      <c r="K171" s="13"/>
-      <c r="L171" s="14"/>
+      <c r="J171" s="21"/>
+      <c r="K171" s="21"/>
+      <c r="L171" s="23"/>
       <c r="N171">
         <f t="shared" si="21"/>
         <v>4.2720000000000002</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A172" s="1"/>
       <c r="B172" s="1">
         <v>7</v>
@@ -12555,15 +12884,15 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="J172" s="13"/>
-      <c r="K172" s="13"/>
-      <c r="L172" s="14"/>
+      <c r="J172" s="21"/>
+      <c r="K172" s="21"/>
+      <c r="L172" s="23"/>
       <c r="N172">
         <f t="shared" si="21"/>
         <v>3.8499999999999996</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A173" s="1"/>
       <c r="B173" s="1">
         <v>8</v>
@@ -12593,15 +12922,15 @@
         <f t="shared" si="20"/>
         <v>-4</v>
       </c>
-      <c r="J173" s="13"/>
-      <c r="K173" s="13"/>
-      <c r="L173" s="14"/>
+      <c r="J173" s="21"/>
+      <c r="K173" s="21"/>
+      <c r="L173" s="23"/>
       <c r="N173">
         <f t="shared" si="21"/>
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A174" s="1"/>
       <c r="B174" s="1">
         <v>9</v>
@@ -12631,15 +12960,15 @@
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
-      <c r="J174" s="13"/>
-      <c r="K174" s="13"/>
-      <c r="L174" s="14"/>
+      <c r="J174" s="21"/>
+      <c r="K174" s="21"/>
+      <c r="L174" s="23"/>
       <c r="N174">
         <f t="shared" si="21"/>
         <v>1.647</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A175" s="1"/>
       <c r="B175" s="1">
         <v>10</v>
@@ -12669,15 +12998,15 @@
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
-      <c r="J175" s="13"/>
-      <c r="K175" s="13"/>
-      <c r="L175" s="14"/>
+      <c r="J175" s="21"/>
+      <c r="K175" s="21"/>
+      <c r="L175" s="23"/>
       <c r="N175">
         <f t="shared" si="21"/>
         <v>2.8699999999999997</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A176" s="1"/>
       <c r="B176" s="1">
         <v>11</v>
@@ -12707,15 +13036,15 @@
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
-      <c r="J176" s="13"/>
-      <c r="K176" s="13"/>
-      <c r="L176" s="14"/>
+      <c r="J176" s="21"/>
+      <c r="K176" s="21"/>
+      <c r="L176" s="23"/>
       <c r="N176">
         <f>F176*D177</f>
         <v>2.9159999999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A177" s="1"/>
       <c r="B177" s="1">
         <v>12</v>
@@ -12745,15 +13074,15 @@
         <f t="shared" si="20"/>
         <v>-4</v>
       </c>
-      <c r="J177" s="13"/>
-      <c r="K177" s="13"/>
-      <c r="L177" s="14"/>
+      <c r="J177" s="21"/>
+      <c r="K177" s="21"/>
+      <c r="L177" s="23"/>
       <c r="N177">
         <f t="shared" si="21"/>
         <v>2.4</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A178" s="1"/>
       <c r="B178" s="1">
         <v>13</v>
@@ -12783,15 +13112,15 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="J178" s="13"/>
-      <c r="K178" s="13"/>
-      <c r="L178" s="14"/>
+      <c r="J178" s="21"/>
+      <c r="K178" s="21"/>
+      <c r="L178" s="23"/>
       <c r="N178">
         <f t="shared" si="21"/>
         <v>2.2050000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A179" s="1"/>
       <c r="B179" s="1">
         <v>14</v>
@@ -12821,15 +13150,15 @@
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="J179" s="13"/>
-      <c r="K179" s="13"/>
-      <c r="L179" s="14"/>
+      <c r="J179" s="21"/>
+      <c r="K179" s="21"/>
+      <c r="L179" s="23"/>
       <c r="N179">
         <f>F179*D180</f>
         <v>4.2749999999999995</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A180" s="1"/>
       <c r="B180" s="1">
         <v>15</v>
@@ -12859,15 +13188,15 @@
         <f t="shared" si="20"/>
         <v>-9</v>
       </c>
-      <c r="J180" s="13"/>
-      <c r="K180" s="13"/>
-      <c r="L180" s="14"/>
+      <c r="J180" s="21"/>
+      <c r="K180" s="21"/>
+      <c r="L180" s="23"/>
       <c r="N180">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -12881,7 +13210,7 @@
       <c r="K181" s="1"/>
       <c r="L181" s="11"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -12894,45 +13223,45 @@
       <c r="J182" s="1"/>
       <c r="K182" s="1"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B183" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C183" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C183" s="1" t="s">
+      <c r="D183" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="E183" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E183" s="1" t="s">
+      <c r="F183" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F183" s="1" t="s">
+      <c r="G183" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G183" s="1" t="s">
+      <c r="H183" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="H183" s="1" t="s">
+      <c r="I183" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I183" s="1" t="s">
+      <c r="J183" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K183" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J183" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K183" s="1" t="s">
+      <c r="L183" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="L183" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A184" s="1"/>
       <c r="B184" s="1">
         <v>1</v>
@@ -12962,20 +13291,20 @@
         <f>G184-H184</f>
         <v>7</v>
       </c>
-      <c r="J184" s="13">
+      <c r="J184" s="21">
         <f>SUM(F184:F198)</f>
         <v>150</v>
       </c>
-      <c r="K184" s="13">
+      <c r="K184" s="21">
         <f>SUM(N185:N198)</f>
         <v>47.798999999999999</v>
       </c>
-      <c r="L184" s="14">
+      <c r="L184" s="23">
         <f>K184/J184</f>
         <v>0.31866</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A185" s="1"/>
       <c r="B185" s="1">
         <v>2</v>
@@ -13005,15 +13334,15 @@
         <f t="shared" ref="I185:I198" si="25">G185-H185</f>
         <v>-3</v>
       </c>
-      <c r="J185" s="13"/>
-      <c r="K185" s="13"/>
-      <c r="L185" s="14"/>
+      <c r="J185" s="21"/>
+      <c r="K185" s="21"/>
+      <c r="L185" s="23"/>
       <c r="N185">
         <f>F184*D185</f>
         <v>3.3249999999999997</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A186" s="1"/>
       <c r="B186" s="1">
         <v>3</v>
@@ -13043,15 +13372,15 @@
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
-      <c r="J186" s="13"/>
-      <c r="K186" s="13"/>
-      <c r="L186" s="14"/>
+      <c r="J186" s="21"/>
+      <c r="K186" s="21"/>
+      <c r="L186" s="23"/>
       <c r="N186">
         <f t="shared" ref="N186:N196" si="27">F185*D186</f>
         <v>1.764</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A187" s="1"/>
       <c r="B187" s="1">
         <v>4</v>
@@ -13081,15 +13410,15 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J187" s="13"/>
-      <c r="K187" s="13"/>
-      <c r="L187" s="14"/>
+      <c r="J187" s="21"/>
+      <c r="K187" s="21"/>
+      <c r="L187" s="23"/>
       <c r="N187">
         <f t="shared" si="27"/>
         <v>2.6999999999999997</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A188" s="1"/>
       <c r="B188" s="1">
         <v>5</v>
@@ -13119,15 +13448,15 @@
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
-      <c r="J188" s="13"/>
-      <c r="K188" s="13"/>
-      <c r="L188" s="14"/>
+      <c r="J188" s="21"/>
+      <c r="K188" s="21"/>
+      <c r="L188" s="23"/>
       <c r="N188">
         <f t="shared" si="27"/>
         <v>2.1869999999999998</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A189" s="1"/>
       <c r="B189" s="1">
         <v>6</v>
@@ -13157,15 +13486,15 @@
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
-      <c r="J189" s="13"/>
-      <c r="K189" s="13"/>
-      <c r="L189" s="14"/>
+      <c r="J189" s="21"/>
+      <c r="K189" s="21"/>
+      <c r="L189" s="23"/>
       <c r="N189">
         <f t="shared" si="27"/>
         <v>4.0179999999999998</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A190" s="1"/>
       <c r="B190" s="1">
         <v>7</v>
@@ -13195,15 +13524,15 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J190" s="13"/>
-      <c r="K190" s="13"/>
-      <c r="L190" s="14"/>
+      <c r="J190" s="21"/>
+      <c r="K190" s="21"/>
+      <c r="L190" s="23"/>
       <c r="N190">
         <f t="shared" si="27"/>
         <v>3.4769999999999999</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A191" s="1"/>
       <c r="B191" s="1">
         <v>8</v>
@@ -13233,15 +13562,15 @@
         <f t="shared" si="25"/>
         <v>-1</v>
       </c>
-      <c r="J191" s="13"/>
-      <c r="K191" s="13"/>
-      <c r="L191" s="14"/>
+      <c r="J191" s="21"/>
+      <c r="K191" s="21"/>
+      <c r="L191" s="23"/>
       <c r="N191">
         <f t="shared" si="27"/>
         <v>7.7899999999999991</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A192" s="1"/>
       <c r="B192" s="1">
         <v>9</v>
@@ -13271,15 +13600,15 @@
         <f t="shared" si="25"/>
         <v>-3</v>
       </c>
-      <c r="J192" s="13"/>
-      <c r="K192" s="13"/>
-      <c r="L192" s="14"/>
+      <c r="J192" s="21"/>
+      <c r="K192" s="21"/>
+      <c r="L192" s="23"/>
       <c r="N192">
         <f t="shared" si="27"/>
         <v>6.3</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A193" s="1"/>
       <c r="B193" s="1">
         <v>10</v>
@@ -13309,15 +13638,15 @@
         <f t="shared" si="25"/>
         <v>-1</v>
       </c>
-      <c r="J193" s="13"/>
-      <c r="K193" s="13"/>
-      <c r="L193" s="14"/>
+      <c r="J193" s="21"/>
+      <c r="K193" s="21"/>
+      <c r="L193" s="23"/>
       <c r="N193">
         <f t="shared" si="27"/>
         <v>5.34</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A194" s="1"/>
       <c r="B194" s="1">
         <v>11</v>
@@ -13347,15 +13676,15 @@
         <f t="shared" si="25"/>
         <v>-4</v>
       </c>
-      <c r="J194" s="13"/>
-      <c r="K194" s="13"/>
-      <c r="L194" s="14"/>
+      <c r="J194" s="21"/>
+      <c r="K194" s="21"/>
+      <c r="L194" s="23"/>
       <c r="N194">
         <f t="shared" si="27"/>
         <v>5.0819999999999999</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A195" s="1"/>
       <c r="B195" s="1">
         <v>12</v>
@@ -13385,15 +13714,15 @@
         <f t="shared" si="25"/>
         <v>-6</v>
       </c>
-      <c r="J195" s="13"/>
-      <c r="K195" s="13"/>
-      <c r="L195" s="14"/>
+      <c r="J195" s="21"/>
+      <c r="K195" s="21"/>
+      <c r="L195" s="23"/>
       <c r="N195">
         <f t="shared" si="27"/>
         <v>3.04</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A196" s="1"/>
       <c r="B196" s="1">
         <v>13</v>
@@ -13423,15 +13752,15 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J196" s="13"/>
-      <c r="K196" s="13"/>
-      <c r="L196" s="14"/>
+      <c r="J196" s="21"/>
+      <c r="K196" s="21"/>
+      <c r="L196" s="23"/>
       <c r="N196">
         <f t="shared" si="27"/>
         <v>0.71599999999999997</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A197" s="1"/>
       <c r="B197" s="1">
         <v>14</v>
@@ -13461,15 +13790,15 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J197" s="13"/>
-      <c r="K197" s="13"/>
-      <c r="L197" s="14"/>
+      <c r="J197" s="21"/>
+      <c r="K197" s="21"/>
+      <c r="L197" s="23"/>
       <c r="N197">
         <f>F196*D197</f>
         <v>1.3720000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A198" s="1"/>
       <c r="B198" s="1">
         <v>15</v>
@@ -13499,15 +13828,15 @@
         <f t="shared" si="25"/>
         <v>-4</v>
       </c>
-      <c r="J198" s="13"/>
-      <c r="K198" s="13"/>
-      <c r="L198" s="14"/>
+      <c r="J198" s="21"/>
+      <c r="K198" s="21"/>
+      <c r="L198" s="23"/>
       <c r="N198">
         <f>F197*D198</f>
         <v>0.68799999999999994</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -13521,7 +13850,7 @@
       <c r="K199" s="1"/>
       <c r="L199" s="11"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -13535,7 +13864,7 @@
       <c r="K200" s="1"/>
       <c r="L200" s="11"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -13549,7 +13878,7 @@
       <c r="K201" s="1"/>
       <c r="L201" s="11"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -13563,7 +13892,7 @@
       <c r="K202" s="1"/>
       <c r="L202" s="11"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -13577,7 +13906,7 @@
       <c r="K203" s="1"/>
       <c r="L203" s="11"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -13591,45 +13920,45 @@
       <c r="K204" s="1"/>
       <c r="L204" s="11"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A219" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C219" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C219" s="1" t="s">
+      <c r="D219" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="E219" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E219" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="F219" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I219" t="s">
+        <v>49</v>
+      </c>
+      <c r="J219" t="s">
+        <v>50</v>
+      </c>
+      <c r="K219" t="s">
+        <v>51</v>
+      </c>
+      <c r="L219" t="s">
+        <v>52</v>
+      </c>
+      <c r="M219" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="H219" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I219" t="s">
-        <v>50</v>
-      </c>
-      <c r="J219" t="s">
-        <v>51</v>
-      </c>
-      <c r="K219" t="s">
-        <v>52</v>
-      </c>
-      <c r="L219" t="s">
-        <v>53</v>
-      </c>
-      <c r="M219" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>1</v>
       </c>
@@ -13645,7 +13974,7 @@
       <c r="E220" s="1">
         <v>7</v>
       </c>
-      <c r="F220" s="13">
+      <c r="F220" s="21">
         <v>142</v>
       </c>
       <c r="H220" s="1">
@@ -13663,12 +13992,12 @@
       <c r="L220">
         <v>7</v>
       </c>
-      <c r="M220" s="13">
+      <c r="M220" s="21">
         <f>SUM(I220:I234)</f>
         <v>150</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>2</v>
       </c>
@@ -13684,7 +14013,7 @@
       <c r="E221" s="1">
         <v>12</v>
       </c>
-      <c r="F221" s="13"/>
+      <c r="F221" s="21"/>
       <c r="H221" s="1">
         <v>2</v>
       </c>
@@ -13700,9 +14029,9 @@
       <c r="L221">
         <v>-3</v>
       </c>
-      <c r="M221" s="13"/>
-    </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M221" s="21"/>
+    </row>
+    <row r="222" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>3</v>
       </c>
@@ -13718,7 +14047,7 @@
       <c r="E222" s="1">
         <v>-8</v>
       </c>
-      <c r="F222" s="13"/>
+      <c r="F222" s="21"/>
       <c r="H222" s="1">
         <v>3</v>
       </c>
@@ -13734,9 +14063,9 @@
       <c r="L222">
         <v>5</v>
       </c>
-      <c r="M222" s="13"/>
-    </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M222" s="21"/>
+    </row>
+    <row r="223" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>4</v>
       </c>
@@ -13752,7 +14081,7 @@
       <c r="E223" s="1">
         <v>-2</v>
       </c>
-      <c r="F223" s="13"/>
+      <c r="F223" s="21"/>
       <c r="H223" s="1">
         <v>4</v>
       </c>
@@ -13768,9 +14097,9 @@
       <c r="L223">
         <v>0</v>
       </c>
-      <c r="M223" s="13"/>
-    </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M223" s="21"/>
+    </row>
+    <row r="224" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>5</v>
       </c>
@@ -13786,7 +14115,7 @@
       <c r="E224" s="1">
         <v>4</v>
       </c>
-      <c r="F224" s="13"/>
+      <c r="F224" s="21"/>
       <c r="H224" s="1">
         <v>5</v>
       </c>
@@ -13802,9 +14131,9 @@
       <c r="L224">
         <v>5</v>
       </c>
-      <c r="M224" s="13"/>
-    </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M224" s="21"/>
+    </row>
+    <row r="225" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>6</v>
       </c>
@@ -13820,7 +14149,7 @@
       <c r="E225" s="1">
         <v>-1</v>
       </c>
-      <c r="F225" s="13"/>
+      <c r="F225" s="21"/>
       <c r="H225" s="1">
         <v>6</v>
       </c>
@@ -13836,9 +14165,9 @@
       <c r="L225">
         <v>5</v>
       </c>
-      <c r="M225" s="13"/>
-    </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M225" s="21"/>
+    </row>
+    <row r="226" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>7</v>
       </c>
@@ -13854,7 +14183,7 @@
       <c r="E226" s="1">
         <v>-1</v>
       </c>
-      <c r="F226" s="13"/>
+      <c r="F226" s="21"/>
       <c r="H226" s="1">
         <v>7</v>
       </c>
@@ -13870,9 +14199,9 @@
       <c r="L226">
         <v>0</v>
       </c>
-      <c r="M226" s="13"/>
-    </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M226" s="21"/>
+    </row>
+    <row r="227" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>8</v>
       </c>
@@ -13888,7 +14217,7 @@
       <c r="E227" s="1">
         <v>-4</v>
       </c>
-      <c r="F227" s="13"/>
+      <c r="F227" s="21"/>
       <c r="H227" s="1">
         <v>8</v>
       </c>
@@ -13904,9 +14233,9 @@
       <c r="L227">
         <v>-1</v>
       </c>
-      <c r="M227" s="13"/>
-    </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M227" s="21"/>
+    </row>
+    <row r="228" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>9</v>
       </c>
@@ -13922,7 +14251,7 @@
       <c r="E228" s="1">
         <v>2</v>
       </c>
-      <c r="F228" s="13"/>
+      <c r="F228" s="21"/>
       <c r="H228" s="1">
         <v>9</v>
       </c>
@@ -13938,9 +14267,9 @@
       <c r="L228">
         <v>-3</v>
       </c>
-      <c r="M228" s="13"/>
-    </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M228" s="21"/>
+    </row>
+    <row r="229" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>10</v>
       </c>
@@ -13956,7 +14285,7 @@
       <c r="E229" s="1">
         <v>1</v>
       </c>
-      <c r="F229" s="13"/>
+      <c r="F229" s="21"/>
       <c r="H229" s="1">
         <v>10</v>
       </c>
@@ -13972,9 +14301,9 @@
       <c r="L229">
         <v>-1</v>
       </c>
-      <c r="M229" s="13"/>
-    </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M229" s="21"/>
+    </row>
+    <row r="230" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>11</v>
       </c>
@@ -13990,7 +14319,7 @@
       <c r="E230" s="1">
         <v>2</v>
       </c>
-      <c r="F230" s="13"/>
+      <c r="F230" s="21"/>
       <c r="H230" s="1">
         <v>11</v>
       </c>
@@ -14006,9 +14335,9 @@
       <c r="L230">
         <v>-4</v>
       </c>
-      <c r="M230" s="13"/>
-    </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M230" s="21"/>
+    </row>
+    <row r="231" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>12</v>
       </c>
@@ -14024,7 +14353,7 @@
       <c r="E231" s="1">
         <v>-4</v>
       </c>
-      <c r="F231" s="13"/>
+      <c r="F231" s="21"/>
       <c r="H231" s="1">
         <v>12</v>
       </c>
@@ -14040,9 +14369,9 @@
       <c r="L231">
         <v>-6</v>
       </c>
-      <c r="M231" s="13"/>
-    </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M231" s="21"/>
+    </row>
+    <row r="232" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>13</v>
       </c>
@@ -14058,7 +14387,7 @@
       <c r="E232" s="1">
         <v>-3</v>
       </c>
-      <c r="F232" s="13"/>
+      <c r="F232" s="21"/>
       <c r="H232" s="1">
         <v>13</v>
       </c>
@@ -14074,9 +14403,9 @@
       <c r="L232">
         <v>0</v>
       </c>
-      <c r="M232" s="13"/>
-    </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M232" s="21"/>
+    </row>
+    <row r="233" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>14</v>
       </c>
@@ -14092,7 +14421,7 @@
       <c r="E233" s="1">
         <v>4</v>
       </c>
-      <c r="F233" s="13"/>
+      <c r="F233" s="21"/>
       <c r="H233" s="1">
         <v>14</v>
       </c>
@@ -14108,9 +14437,9 @@
       <c r="L233">
         <v>0</v>
       </c>
-      <c r="M233" s="13"/>
-    </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M233" s="21"/>
+    </row>
+    <row r="234" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>15</v>
       </c>
@@ -14126,7 +14455,7 @@
       <c r="E234" s="1">
         <v>-9</v>
       </c>
-      <c r="F234" s="13"/>
+      <c r="F234" s="21"/>
       <c r="H234" s="1">
         <v>15</v>
       </c>
@@ -14142,10 +14471,10 @@
       <c r="L234">
         <v>-4</v>
       </c>
-      <c r="M234" s="13"/>
+      <c r="M234" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
     <mergeCell ref="F220:F234"/>
     <mergeCell ref="M220:M234"/>
     <mergeCell ref="J166:J180"/>
@@ -14154,9 +14483,1911 @@
     <mergeCell ref="K184:K198"/>
     <mergeCell ref="L166:L180"/>
     <mergeCell ref="L184:L198"/>
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF8E1CDB-B36D-49F0-8622-B854A9A0A129}">
+  <dimension ref="A1:O64"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="14">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="C2" s="14">
+        <v>19.149999999999999</v>
+      </c>
+      <c r="D2" s="14">
+        <v>4</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A3" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="14">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="C3" s="14">
+        <v>19.170000000000002</v>
+      </c>
+      <c r="D3" s="14">
+        <v>0</v>
+      </c>
+      <c r="E3" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A4" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="14">
+        <v>19.18</v>
+      </c>
+      <c r="C4" s="14">
+        <v>19.190000000000001</v>
+      </c>
+      <c r="D4" s="14">
+        <v>3</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="14">
+        <v>19.2</v>
+      </c>
+      <c r="C5" s="14">
+        <v>19.21</v>
+      </c>
+      <c r="D5" s="14">
+        <v>1</v>
+      </c>
+      <c r="E5" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A6" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="14">
+        <v>19.22</v>
+      </c>
+      <c r="C6" s="14">
+        <v>19.23</v>
+      </c>
+      <c r="D6" s="14">
+        <v>2</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="O6" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="14">
+        <v>19.25</v>
+      </c>
+      <c r="C7" s="14">
+        <v>19.25</v>
+      </c>
+      <c r="D7" s="14">
+        <v>4</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="17">
+        <v>18.02</v>
+      </c>
+      <c r="M7" s="17">
+        <v>18.02</v>
+      </c>
+      <c r="N7" s="17">
+        <v>3</v>
+      </c>
+      <c r="O7" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A8" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="14">
+        <v>19.28</v>
+      </c>
+      <c r="C8" s="14">
+        <v>19.29</v>
+      </c>
+      <c r="D8" s="14">
+        <v>0</v>
+      </c>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L8" s="17">
+        <v>18.04</v>
+      </c>
+      <c r="M8" s="17">
+        <v>18.04</v>
+      </c>
+      <c r="N8" s="17">
+        <v>5</v>
+      </c>
+      <c r="O8" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="14">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="C9" s="14">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="D9" s="14">
+        <v>1</v>
+      </c>
+      <c r="E9" s="14">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="17">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="M9" s="17">
+        <v>18.07</v>
+      </c>
+      <c r="N9" s="17">
+        <v>0</v>
+      </c>
+      <c r="O9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A10" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="14">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="C10" s="14">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="D10" s="14">
+        <v>2</v>
+      </c>
+      <c r="E10" s="14">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="17">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="M10" s="17">
+        <v>18.09</v>
+      </c>
+      <c r="N10" s="17">
+        <v>1</v>
+      </c>
+      <c r="O10" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="14">
+        <v>19.37</v>
+      </c>
+      <c r="C11" s="14">
+        <v>19.38</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="17">
+        <v>18.12</v>
+      </c>
+      <c r="M11" s="17">
+        <v>18.13</v>
+      </c>
+      <c r="N11" s="17">
+        <v>3</v>
+      </c>
+      <c r="O11" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A12" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="14">
+        <v>19.43</v>
+      </c>
+      <c r="C12" s="14">
+        <v>19.43</v>
+      </c>
+      <c r="D12" s="14">
+        <v>0</v>
+      </c>
+      <c r="E12" s="14">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="17">
+        <v>18.18</v>
+      </c>
+      <c r="M12" s="17">
+        <v>18.190000000000001</v>
+      </c>
+      <c r="N12" s="17">
+        <v>1</v>
+      </c>
+      <c r="O12" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A13" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="14">
+        <v>19.46</v>
+      </c>
+      <c r="C13" s="14">
+        <v>19.46</v>
+      </c>
+      <c r="D13" s="14">
+        <v>5</v>
+      </c>
+      <c r="E13" s="14">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <v>7</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L13" s="17">
+        <v>18.23</v>
+      </c>
+      <c r="M13" s="17">
+        <v>18.23</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14">
+        <v>19.48</v>
+      </c>
+      <c r="C14" s="14">
+        <v>19.48</v>
+      </c>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="14">
+        <v>4</v>
+      </c>
+      <c r="J14">
+        <v>8</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="17">
+        <v>18.25</v>
+      </c>
+      <c r="M14" s="17">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="N14" s="17">
+        <v>1</v>
+      </c>
+      <c r="O14" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="C15" s="14">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="D15" s="14">
+        <v>3</v>
+      </c>
+      <c r="E15" s="14">
+        <v>2</v>
+      </c>
+      <c r="J15">
+        <v>9</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="17">
+        <v>18.28</v>
+      </c>
+      <c r="M15" s="17">
+        <v>18.28</v>
+      </c>
+      <c r="N15" s="17">
+        <v>1</v>
+      </c>
+      <c r="O15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A16" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="14">
+        <v>19.53</v>
+      </c>
+      <c r="C16" s="14">
+        <v>19.53</v>
+      </c>
+      <c r="D16" s="14">
+        <v>0</v>
+      </c>
+      <c r="E16" s="14">
+        <v>2</v>
+      </c>
+      <c r="J16">
+        <v>10</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L16" s="17">
+        <v>18.3</v>
+      </c>
+      <c r="M16" s="17">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="N16" s="17">
+        <v>2</v>
+      </c>
+      <c r="O16" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14">
+        <v>27</v>
+      </c>
+      <c r="E17" s="14">
+        <v>27</v>
+      </c>
+      <c r="J17">
+        <v>11</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17" s="17">
+        <v>18.329999999999998</v>
+      </c>
+      <c r="M17" s="17">
+        <v>18.34</v>
+      </c>
+      <c r="N17" s="17">
+        <v>2</v>
+      </c>
+      <c r="O17" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="J18">
+        <v>12</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="17">
+        <v>18.36</v>
+      </c>
+      <c r="M18" s="17">
+        <v>18.37</v>
+      </c>
+      <c r="N18" s="17">
+        <v>0</v>
+      </c>
+      <c r="O18" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="J19">
+        <v>13</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19" s="17">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M19" s="17">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="N19" s="17">
+        <v>0</v>
+      </c>
+      <c r="O19" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="J20">
+        <v>14</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="17">
+        <v>18.41</v>
+      </c>
+      <c r="M20" s="17">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="N20" s="17">
+        <v>2</v>
+      </c>
+      <c r="O20" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="J21">
+        <v>15</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="17">
+        <v>18.43</v>
+      </c>
+      <c r="M21" s="17">
+        <v>18.43</v>
+      </c>
+      <c r="N21" s="17">
+        <v>0</v>
+      </c>
+      <c r="O21" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A22" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="17"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17">
+        <v>21</v>
+      </c>
+      <c r="O22" s="17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A23" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="14">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="C23" s="14">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A24" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="14">
+        <v>19.36</v>
+      </c>
+      <c r="C24" s="14">
+        <v>19.37</v>
+      </c>
+      <c r="D24" s="14">
+        <v>0</v>
+      </c>
+      <c r="E24" s="14">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>0</v>
+      </c>
+      <c r="K24" s="17"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="17"/>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A25" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="14">
+        <v>19.38</v>
+      </c>
+      <c r="C25" s="14">
+        <v>19.38</v>
+      </c>
+      <c r="D25" s="14">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A26" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="14">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="C26" s="14">
+        <v>19.41</v>
+      </c>
+      <c r="D26" s="14">
+        <v>0</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>68</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M26" s="17"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A27" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="14">
+        <v>19.43</v>
+      </c>
+      <c r="C27" s="14">
+        <v>19.43</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="O27" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28" s="14">
+        <v>19.45</v>
+      </c>
+      <c r="C28" s="14">
+        <v>19.46</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="14">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="17">
+        <v>18.03</v>
+      </c>
+      <c r="M28" s="17">
+        <v>18.03</v>
+      </c>
+      <c r="N28" s="17">
+        <v>2</v>
+      </c>
+      <c r="O28" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A29" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" s="14">
+        <v>19.489999999999998</v>
+      </c>
+      <c r="C29" s="14">
+        <v>19.5</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="17">
+        <v>18.05</v>
+      </c>
+      <c r="M29" s="17">
+        <v>18.05</v>
+      </c>
+      <c r="N29" s="17">
+        <v>6</v>
+      </c>
+      <c r="O29" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A30" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="14">
+        <v>19.52</v>
+      </c>
+      <c r="C30" s="14">
+        <v>19.52</v>
+      </c>
+      <c r="D30" s="14">
+        <v>0</v>
+      </c>
+      <c r="E30" s="14">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>3</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="17">
+        <v>18.07</v>
+      </c>
+      <c r="M30" s="17">
+        <v>18.080000000000002</v>
+      </c>
+      <c r="N30" s="17">
+        <v>1</v>
+      </c>
+      <c r="O30" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A31" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="14">
+        <v>19.54</v>
+      </c>
+      <c r="C31" s="14">
+        <v>19.55</v>
+      </c>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="14">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>4</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="17">
+        <v>18.09</v>
+      </c>
+      <c r="M31" s="17">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="N31" s="17">
+        <v>0</v>
+      </c>
+      <c r="O31" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A32" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="14">
+        <v>19.579999999999998</v>
+      </c>
+      <c r="C32" s="14">
+        <v>19.59</v>
+      </c>
+      <c r="D32" s="14">
+        <v>0</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>5</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L32" s="17">
+        <v>18.130000000000003</v>
+      </c>
+      <c r="M32" s="17">
+        <v>18.14</v>
+      </c>
+      <c r="N32" s="17">
+        <v>3</v>
+      </c>
+      <c r="O32" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A33" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="14">
+        <v>20.02</v>
+      </c>
+      <c r="C33" s="14">
+        <v>20.03</v>
+      </c>
+      <c r="D33" s="14">
+        <v>2</v>
+      </c>
+      <c r="E33" s="14">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>6</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="17">
+        <v>18.190000000000001</v>
+      </c>
+      <c r="M33" s="17">
+        <v>18.200000000000003</v>
+      </c>
+      <c r="N33" s="17">
+        <v>1</v>
+      </c>
+      <c r="O33" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A34" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="14">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="D34" s="14">
+        <v>0</v>
+      </c>
+      <c r="E34" s="14">
+        <v>5</v>
+      </c>
+      <c r="J34">
+        <v>7</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L34" s="17">
+        <v>18.240000000000002</v>
+      </c>
+      <c r="M34" s="17">
+        <v>18.240000000000002</v>
+      </c>
+      <c r="N34" s="17">
+        <v>0</v>
+      </c>
+      <c r="O34" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A35" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="14">
+        <v>20.079999999999998</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20.079999999999998</v>
+      </c>
+      <c r="D35" s="14">
+        <v>1</v>
+      </c>
+      <c r="E35" s="14">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>8</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L35" s="17">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="M35" s="17">
+        <v>18.270000000000003</v>
+      </c>
+      <c r="N35" s="17">
+        <v>1</v>
+      </c>
+      <c r="O35" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A36" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="14">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="C36" s="14">
+        <v>20.11</v>
+      </c>
+      <c r="D36" s="14">
+        <v>1</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>9</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="17">
+        <v>18.290000000000003</v>
+      </c>
+      <c r="M36" s="17">
+        <v>18.290000000000003</v>
+      </c>
+      <c r="N36" s="17">
+        <v>0</v>
+      </c>
+      <c r="O36" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A37" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="14">
+        <v>20.13</v>
+      </c>
+      <c r="C37" s="14">
+        <v>20.13</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>1</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L37" s="17">
+        <v>18.310000000000002</v>
+      </c>
+      <c r="M37" s="17">
+        <v>18.32</v>
+      </c>
+      <c r="N37" s="17">
+        <v>2</v>
+      </c>
+      <c r="O37" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14">
+        <v>14</v>
+      </c>
+      <c r="E38" s="14">
+        <v>14</v>
+      </c>
+      <c r="J38">
+        <v>11</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38" s="17">
+        <v>18.34</v>
+      </c>
+      <c r="M38" s="17">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="N38" s="17">
+        <v>0</v>
+      </c>
+      <c r="O38" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="J39">
+        <v>12</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L39" s="17">
+        <v>18.37</v>
+      </c>
+      <c r="M39" s="17">
+        <v>18.380000000000003</v>
+      </c>
+      <c r="N39" s="17">
+        <v>0</v>
+      </c>
+      <c r="O39" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="J40">
+        <v>13</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L40" s="17">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="M40" s="17">
+        <v>18.41</v>
+      </c>
+      <c r="N40" s="17">
+        <v>0</v>
+      </c>
+      <c r="O40" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="J41">
+        <v>14</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L41" s="17">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="M41" s="17">
+        <v>18.430000000000003</v>
+      </c>
+      <c r="N41" s="17">
+        <v>3</v>
+      </c>
+      <c r="O41" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="J42">
+        <v>15</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="17">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="M42" s="17">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="N42" s="17">
+        <v>0</v>
+      </c>
+      <c r="O42" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A43" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17">
+        <v>19</v>
+      </c>
+      <c r="O43" s="17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A44" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="14">
+        <v>20.05</v>
+      </c>
+      <c r="C44" s="14">
+        <v>20.05</v>
+      </c>
+      <c r="D44" s="14">
+        <v>2</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A45" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="14">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="C45" s="14">
+        <v>20.059999999999999</v>
+      </c>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <v>1</v>
+      </c>
+      <c r="J45" t="s">
+        <v>0</v>
+      </c>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A46" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B46" s="14">
+        <v>20.07</v>
+      </c>
+      <c r="C46" s="14">
+        <v>20.079999999999998</v>
+      </c>
+      <c r="D46" s="14">
+        <v>1</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>1</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A47" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="14">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="C47" s="14">
+        <v>20.11</v>
+      </c>
+      <c r="D47" s="14">
+        <v>1</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>68</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="M47" s="17"/>
+      <c r="N47" s="17"/>
+      <c r="O47" s="17"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" s="14">
+        <v>20.13</v>
+      </c>
+      <c r="C48" s="14">
+        <v>20.13</v>
+      </c>
+      <c r="D48" s="14">
+        <v>1</v>
+      </c>
+      <c r="E48" s="14">
+        <v>1</v>
+      </c>
+      <c r="J48" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="M48" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="O48" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A49" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="14">
+        <v>20.149999999999999</v>
+      </c>
+      <c r="C49" s="14">
+        <v>20.16</v>
+      </c>
+      <c r="D49" s="14">
+        <v>1</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L49" s="17">
+        <v>18.040000000000003</v>
+      </c>
+      <c r="M49" s="17">
+        <v>18.040000000000003</v>
+      </c>
+      <c r="N49" s="17">
+        <v>2</v>
+      </c>
+      <c r="O49" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A50" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="14">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="C50" s="14">
+        <v>20.190000000000001</v>
+      </c>
+      <c r="D50" s="14">
+        <v>2</v>
+      </c>
+      <c r="E50" s="14">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>2</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L50" s="17">
+        <v>18.060000000000002</v>
+      </c>
+      <c r="M50" s="17">
+        <v>18.060000000000002</v>
+      </c>
+      <c r="N50" s="17">
+        <v>4</v>
+      </c>
+      <c r="O50" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A51" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="14">
+        <v>20.21</v>
+      </c>
+      <c r="C51" s="14">
+        <v>20.21</v>
+      </c>
+      <c r="D51" s="14">
+        <v>0</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>3</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="L51" s="17">
+        <v>18.080000000000002</v>
+      </c>
+      <c r="M51" s="17">
+        <v>18.09</v>
+      </c>
+      <c r="N51" s="17">
+        <v>1</v>
+      </c>
+      <c r="O51" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A52" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="14">
+        <v>20.23</v>
+      </c>
+      <c r="C52" s="14">
+        <v>20.23</v>
+      </c>
+      <c r="D52" s="14">
+        <v>1</v>
+      </c>
+      <c r="E52" s="14">
+        <v>2</v>
+      </c>
+      <c r="J52">
+        <v>4</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="17">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="M52" s="17">
+        <v>18.110000000000003</v>
+      </c>
+      <c r="N52" s="17">
+        <v>0</v>
+      </c>
+      <c r="O52" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A53" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" s="14">
+        <v>20.260000000000002</v>
+      </c>
+      <c r="C53" s="14">
+        <v>20.27</v>
+      </c>
+      <c r="D53" s="14">
+        <v>1</v>
+      </c>
+      <c r="E53" s="14">
+        <v>2</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L53" s="17">
+        <v>18.140000000000004</v>
+      </c>
+      <c r="M53" s="17">
+        <v>18.14</v>
+      </c>
+      <c r="N53" s="17">
+        <v>3</v>
+      </c>
+      <c r="O53" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A54" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" s="14">
+        <v>20.309999999999999</v>
+      </c>
+      <c r="C54" s="14">
+        <v>20.309999999999999</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>6</v>
+      </c>
+      <c r="K54" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L54" s="17">
+        <v>18.200000000000003</v>
+      </c>
+      <c r="M54" s="17">
+        <v>18.210000000000004</v>
+      </c>
+      <c r="N54" s="17">
+        <v>0</v>
+      </c>
+      <c r="O54" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A55" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="14">
+        <v>20.34</v>
+      </c>
+      <c r="C55" s="14">
+        <v>20.34</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>3</v>
+      </c>
+      <c r="J55">
+        <v>7</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="L55" s="17">
+        <v>18.250000000000004</v>
+      </c>
+      <c r="M55" s="17">
+        <v>18.250000000000004</v>
+      </c>
+      <c r="N55" s="17">
+        <v>1</v>
+      </c>
+      <c r="O55" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A56" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" s="14">
+        <v>20.350000000000001</v>
+      </c>
+      <c r="C56" s="14">
+        <v>20.36</v>
+      </c>
+      <c r="D56" s="14">
+        <v>3</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>8</v>
+      </c>
+      <c r="K56" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L56" s="17">
+        <v>18.270000000000003</v>
+      </c>
+      <c r="M56" s="17">
+        <v>18.27</v>
+      </c>
+      <c r="N56" s="17">
+        <v>0</v>
+      </c>
+      <c r="O56" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A57" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B57" s="14">
+        <v>20.39</v>
+      </c>
+      <c r="C57" s="14">
+        <v>20.39</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>2</v>
+      </c>
+      <c r="J57">
+        <v>9</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="17">
+        <v>18.300000000000004</v>
+      </c>
+      <c r="M57" s="17">
+        <v>18.300000000000004</v>
+      </c>
+      <c r="N57" s="17">
+        <v>2</v>
+      </c>
+      <c r="O57" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A58" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="14">
+        <v>20.41</v>
+      </c>
+      <c r="C58" s="14">
+        <v>20.41</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>1</v>
+      </c>
+      <c r="J58">
+        <v>10</v>
+      </c>
+      <c r="K58" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="L58" s="17">
+        <v>18.320000000000004</v>
+      </c>
+      <c r="M58" s="17">
+        <v>18.330000000000002</v>
+      </c>
+      <c r="N58" s="17">
+        <v>0</v>
+      </c>
+      <c r="O58" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
+      <c r="C59" s="14"/>
+      <c r="D59" s="14">
+        <v>13</v>
+      </c>
+      <c r="E59" s="14">
+        <v>13</v>
+      </c>
+      <c r="J59">
+        <v>11</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="17">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="M59" s="17">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="N59" s="17">
+        <v>2</v>
+      </c>
+      <c r="O59" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="J60">
+        <v>12</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" s="17">
+        <v>18.380000000000003</v>
+      </c>
+      <c r="M60" s="17">
+        <v>18.38</v>
+      </c>
+      <c r="N60" s="17">
+        <v>0</v>
+      </c>
+      <c r="O60" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="J61">
+        <v>13</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="L61" s="17">
+        <v>18.41</v>
+      </c>
+      <c r="M61" s="17">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="N61" s="17">
+        <v>1</v>
+      </c>
+      <c r="O61" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="J62">
+        <v>14</v>
+      </c>
+      <c r="K62" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="L62" s="17">
+        <v>18.430000000000003</v>
+      </c>
+      <c r="M62" s="17">
+        <v>18.43</v>
+      </c>
+      <c r="N62" s="17">
+        <v>0</v>
+      </c>
+      <c r="O62" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="J63">
+        <v>15</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L63" s="17">
+        <v>18.450000000000003</v>
+      </c>
+      <c r="M63" s="17">
+        <v>18.450000000000003</v>
+      </c>
+      <c r="N63" s="17">
+        <v>0</v>
+      </c>
+      <c r="O63" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.15">
+      <c r="J64" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" s="17"/>
+      <c r="L64" s="17"/>
+      <c r="M64" s="17"/>
+      <c r="N64" s="17">
+        <v>16</v>
+      </c>
+      <c r="O64" s="17">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/晚高峰客流量调查数据1.xlsx
+++ b/晚高峰客流量调查数据1.xlsx
@@ -16,9 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -469,6 +466,18 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -478,19 +487,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7448,209 +7445,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="67">
-          <cell r="B67" t="str">
-            <v>途径站点</v>
-          </cell>
-          <cell r="C67" t="str">
-            <v>上车人数</v>
-          </cell>
-          <cell r="D67" t="str">
-            <v>下车人数</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="B68" t="str">
-            <v>东体育馆</v>
-          </cell>
-          <cell r="C68">
-            <v>4</v>
-          </cell>
-          <cell r="D68">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="B69" t="str">
-            <v>融园东</v>
-          </cell>
-          <cell r="C69">
-            <v>17</v>
-          </cell>
-          <cell r="D69">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="B70" t="str">
-            <v>第三食堂</v>
-          </cell>
-          <cell r="C70">
-            <v>5</v>
-          </cell>
-          <cell r="D70">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="B71" t="str">
-            <v>秀园</v>
-          </cell>
-          <cell r="C71">
-            <v>1</v>
-          </cell>
-          <cell r="D71">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="B72" t="str">
-            <v>第二食堂</v>
-          </cell>
-          <cell r="C72">
-            <v>4</v>
-          </cell>
-          <cell r="D72">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="B73" t="str">
-            <v>综合楼</v>
-          </cell>
-          <cell r="C73">
-            <v>0</v>
-          </cell>
-          <cell r="D73">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="B74" t="str">
-            <v>一食堂</v>
-          </cell>
-          <cell r="C74">
-            <v>2</v>
-          </cell>
-          <cell r="D74">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="B75" t="str">
-            <v>西门</v>
-          </cell>
-          <cell r="C75">
-            <v>2</v>
-          </cell>
-          <cell r="D75">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="B76" t="str">
-            <v>纺化楼</v>
-          </cell>
-          <cell r="C76">
-            <v>0</v>
-          </cell>
-          <cell r="D76">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="B77" t="str">
-            <v>11号教学楼</v>
-          </cell>
-          <cell r="C77">
-            <v>3</v>
-          </cell>
-          <cell r="D77">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="B78" t="str">
-            <v>1号教学楼</v>
-          </cell>
-          <cell r="C78">
-            <v>4</v>
-          </cell>
-          <cell r="D78">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="B79" t="str">
-            <v>逸夫楼</v>
-          </cell>
-          <cell r="C79">
-            <v>1</v>
-          </cell>
-          <cell r="D79">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="B80" t="str">
-            <v>理科楼</v>
-          </cell>
-          <cell r="C80">
-            <v>0</v>
-          </cell>
-          <cell r="D80">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="B81" t="str">
-            <v>东操场</v>
-          </cell>
-          <cell r="C81">
-            <v>0</v>
-          </cell>
-          <cell r="D81">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="B82" t="str">
-            <v>东体育馆</v>
-          </cell>
-          <cell r="C82">
-            <v>0</v>
-          </cell>
-          <cell r="D82">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="C83">
-            <v>43</v>
-          </cell>
-          <cell r="D83">
-            <v>43</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -7926,14 +7720,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -7944,13 +7738,13 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -7961,15 +7755,15 @@
       <c r="A3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="22"/>
+      <c r="F3" s="25"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -9931,19 +9725,19 @@
       <c r="K63" s="1"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="20"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="24"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="18" t="s">
+      <c r="F64" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="20"/>
+      <c r="G64" s="23"/>
+      <c r="H64" s="23"/>
+      <c r="I64" s="24"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
     </row>
@@ -10831,18 +10625,18 @@
       <c r="K105" s="1"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A106" s="24" t="s">
+      <c r="A106" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="18" t="s">
         <v>36</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
-      <c r="E106" s="24" t="s">
+      <c r="E106" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F106" s="24" t="s">
+      <c r="F106" s="18" t="s">
         <v>36</v>
       </c>
       <c r="G106" s="1"/>
@@ -10852,19 +10646,19 @@
       <c r="K106" s="1"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A107" s="25" t="s">
+      <c r="A107" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B107" s="24">
+      <c r="B107" s="18">
         <f>C68-D68</f>
         <v>7</v>
       </c>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
-      <c r="E107" s="25" t="s">
+      <c r="E107" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F107" s="24">
+      <c r="F107" s="18">
         <f>H68-I68</f>
         <v>7</v>
       </c>
@@ -10875,19 +10669,19 @@
       <c r="K107" s="1"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A108" s="25" t="s">
+      <c r="A108" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B108" s="24">
+      <c r="B108" s="18">
         <f>B107+C69-D69</f>
         <v>19</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
-      <c r="E108" s="25" t="s">
+      <c r="E108" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F108" s="24">
+      <c r="F108" s="18">
         <f>F107+H69-I69</f>
         <v>4</v>
       </c>
@@ -10898,19 +10692,19 @@
       <c r="K108" s="1"/>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A109" s="25" t="s">
+      <c r="A109" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B109" s="24">
+      <c r="B109" s="18">
         <f t="shared" ref="B109:B121" si="8">B108+C70-D70</f>
         <v>11</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
-      <c r="E109" s="25" t="s">
+      <c r="E109" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F109" s="24">
+      <c r="F109" s="18">
         <f t="shared" ref="F109:F121" si="9">F108+H70-I70</f>
         <v>9</v>
       </c>
@@ -10921,19 +10715,19 @@
       <c r="K109" s="1"/>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A110" s="25" t="s">
+      <c r="A110" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B110" s="24">
+      <c r="B110" s="18">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
-      <c r="E110" s="25" t="s">
+      <c r="E110" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F110" s="24">
+      <c r="F110" s="18">
         <f t="shared" si="9"/>
         <v>9</v>
       </c>
@@ -10944,19 +10738,19 @@
       <c r="K110" s="1"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A111" s="25" t="s">
+      <c r="A111" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B111" s="24">
+      <c r="B111" s="18">
         <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
-      <c r="E111" s="25" t="s">
+      <c r="E111" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="F111" s="24">
+      <c r="F111" s="18">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
@@ -10967,19 +10761,19 @@
       <c r="K111" s="1"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A112" s="25" t="s">
+      <c r="A112" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B112" s="24">
+      <c r="B112" s="18">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
-      <c r="E112" s="25" t="s">
+      <c r="E112" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F112" s="24">
+      <c r="F112" s="18">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
@@ -10990,19 +10784,19 @@
       <c r="K112" s="1"/>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A113" s="25" t="s">
+      <c r="A113" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B113" s="24">
+      <c r="B113" s="18">
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
-      <c r="E113" s="25" t="s">
+      <c r="E113" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F113" s="24">
+      <c r="F113" s="18">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
@@ -11013,19 +10807,19 @@
       <c r="K113" s="1"/>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A114" s="25" t="s">
+      <c r="A114" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B114" s="24">
+      <c r="B114" s="18">
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
-      <c r="E114" s="25" t="s">
+      <c r="E114" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F114" s="24">
+      <c r="F114" s="18">
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
@@ -11036,19 +10830,19 @@
       <c r="K114" s="1"/>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A115" s="25" t="s">
+      <c r="A115" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B115" s="24">
+      <c r="B115" s="18">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
-      <c r="E115" s="25" t="s">
+      <c r="E115" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F115" s="24">
+      <c r="F115" s="18">
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
@@ -11059,19 +10853,19 @@
       <c r="K115" s="1"/>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A116" s="25" t="s">
+      <c r="A116" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B116" s="24">
+      <c r="B116" s="18">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
-      <c r="E116" s="25" t="s">
+      <c r="E116" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F116" s="24">
+      <c r="F116" s="18">
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
@@ -11082,19 +10876,19 @@
       <c r="K116" s="1"/>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A117" s="25" t="s">
+      <c r="A117" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B117" s="24">
+      <c r="B117" s="18">
         <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
-      <c r="E117" s="25" t="s">
+      <c r="E117" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F117" s="24">
+      <c r="F117" s="18">
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
@@ -11105,19 +10899,19 @@
       <c r="K117" s="1"/>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A118" s="25" t="s">
+      <c r="A118" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B118" s="24">
+      <c r="B118" s="18">
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
-      <c r="E118" s="25" t="s">
+      <c r="E118" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F118" s="24">
+      <c r="F118" s="18">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -11128,19 +10922,19 @@
       <c r="K118" s="1"/>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A119" s="25" t="s">
+      <c r="A119" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B119" s="24">
+      <c r="B119" s="18">
         <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
-      <c r="E119" s="25" t="s">
+      <c r="E119" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F119" s="24">
+      <c r="F119" s="18">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -11151,19 +10945,19 @@
       <c r="K119" s="1"/>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A120" s="25" t="s">
+      <c r="A120" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B120" s="24">
+      <c r="B120" s="18">
         <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
-      <c r="E120" s="25" t="s">
+      <c r="E120" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F120" s="24">
+      <c r="F120" s="18">
         <f t="shared" si="9"/>
         <v>4</v>
       </c>
@@ -11174,19 +10968,19 @@
       <c r="K120" s="1"/>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A121" s="25" t="s">
+      <c r="A121" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B121" s="24">
+      <c r="B121" s="18">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
-      <c r="E121" s="25" t="s">
+      <c r="E121" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F121" s="24">
+      <c r="F121" s="18">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
@@ -12647,15 +12441,15 @@
         <f>G166-H166</f>
         <v>7</v>
       </c>
-      <c r="J166" s="21">
+      <c r="J166" s="20">
         <f>SUM(F166:F180)</f>
         <v>142</v>
       </c>
-      <c r="K166" s="21">
+      <c r="K166" s="20">
         <f>SUM(N166:N179)</f>
         <v>44.449999999999989</v>
       </c>
-      <c r="L166" s="23">
+      <c r="L166" s="21">
         <f>K166/J166</f>
         <v>0.31302816901408442</v>
       </c>
@@ -12694,9 +12488,9 @@
         <f t="shared" ref="I167:I180" si="20">G167-H167</f>
         <v>12</v>
       </c>
-      <c r="J167" s="21"/>
-      <c r="K167" s="21"/>
-      <c r="L167" s="23"/>
+      <c r="J167" s="20"/>
+      <c r="K167" s="20"/>
+      <c r="L167" s="21"/>
       <c r="N167">
         <f t="shared" ref="N167:N180" si="21">F167*D168</f>
         <v>6.5170000000000003</v>
@@ -12732,9 +12526,9 @@
         <f t="shared" si="20"/>
         <v>-8</v>
       </c>
-      <c r="J168" s="21"/>
-      <c r="K168" s="21"/>
-      <c r="L168" s="23"/>
+      <c r="J168" s="20"/>
+      <c r="K168" s="20"/>
+      <c r="L168" s="21"/>
       <c r="N168">
         <f t="shared" si="21"/>
         <v>1.9689999999999999</v>
@@ -12770,9 +12564,9 @@
         <f t="shared" si="20"/>
         <v>-2</v>
       </c>
-      <c r="J169" s="21"/>
-      <c r="K169" s="21"/>
-      <c r="L169" s="23"/>
+      <c r="J169" s="20"/>
+      <c r="K169" s="20"/>
+      <c r="L169" s="21"/>
       <c r="N169">
         <f t="shared" si="21"/>
         <v>2.7359999999999998</v>
@@ -12808,9 +12602,9 @@
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="J170" s="21"/>
-      <c r="K170" s="21"/>
-      <c r="L170" s="23"/>
+      <c r="J170" s="20"/>
+      <c r="K170" s="20"/>
+      <c r="L170" s="21"/>
       <c r="N170">
         <f t="shared" si="21"/>
         <v>4.7189999999999994</v>
@@ -12846,9 +12640,9 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="J171" s="21"/>
-      <c r="K171" s="21"/>
-      <c r="L171" s="23"/>
+      <c r="J171" s="20"/>
+      <c r="K171" s="20"/>
+      <c r="L171" s="21"/>
       <c r="N171">
         <f t="shared" si="21"/>
         <v>4.2720000000000002</v>
@@ -12884,9 +12678,9 @@
         <f t="shared" si="20"/>
         <v>-1</v>
       </c>
-      <c r="J172" s="21"/>
-      <c r="K172" s="21"/>
-      <c r="L172" s="23"/>
+      <c r="J172" s="20"/>
+      <c r="K172" s="20"/>
+      <c r="L172" s="21"/>
       <c r="N172">
         <f t="shared" si="21"/>
         <v>3.8499999999999996</v>
@@ -12922,9 +12716,9 @@
         <f t="shared" si="20"/>
         <v>-4</v>
       </c>
-      <c r="J173" s="21"/>
-      <c r="K173" s="21"/>
-      <c r="L173" s="23"/>
+      <c r="J173" s="20"/>
+      <c r="K173" s="20"/>
+      <c r="L173" s="21"/>
       <c r="N173">
         <f t="shared" si="21"/>
         <v>2.8699999999999997</v>
@@ -12960,9 +12754,9 @@
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
-      <c r="J174" s="21"/>
-      <c r="K174" s="21"/>
-      <c r="L174" s="23"/>
+      <c r="J174" s="20"/>
+      <c r="K174" s="20"/>
+      <c r="L174" s="21"/>
       <c r="N174">
         <f t="shared" si="21"/>
         <v>1.647</v>
@@ -12998,9 +12792,9 @@
         <f t="shared" si="20"/>
         <v>1</v>
       </c>
-      <c r="J175" s="21"/>
-      <c r="K175" s="21"/>
-      <c r="L175" s="23"/>
+      <c r="J175" s="20"/>
+      <c r="K175" s="20"/>
+      <c r="L175" s="21"/>
       <c r="N175">
         <f t="shared" si="21"/>
         <v>2.8699999999999997</v>
@@ -13036,9 +12830,9 @@
         <f t="shared" si="20"/>
         <v>2</v>
       </c>
-      <c r="J176" s="21"/>
-      <c r="K176" s="21"/>
-      <c r="L176" s="23"/>
+      <c r="J176" s="20"/>
+      <c r="K176" s="20"/>
+      <c r="L176" s="21"/>
       <c r="N176">
         <f>F176*D177</f>
         <v>2.9159999999999999</v>
@@ -13074,9 +12868,9 @@
         <f t="shared" si="20"/>
         <v>-4</v>
       </c>
-      <c r="J177" s="21"/>
-      <c r="K177" s="21"/>
-      <c r="L177" s="23"/>
+      <c r="J177" s="20"/>
+      <c r="K177" s="20"/>
+      <c r="L177" s="21"/>
       <c r="N177">
         <f t="shared" si="21"/>
         <v>2.4</v>
@@ -13112,9 +12906,9 @@
         <f t="shared" si="20"/>
         <v>-3</v>
       </c>
-      <c r="J178" s="21"/>
-      <c r="K178" s="21"/>
-      <c r="L178" s="23"/>
+      <c r="J178" s="20"/>
+      <c r="K178" s="20"/>
+      <c r="L178" s="21"/>
       <c r="N178">
         <f t="shared" si="21"/>
         <v>2.2050000000000001</v>
@@ -13150,9 +12944,9 @@
         <f t="shared" si="20"/>
         <v>4</v>
       </c>
-      <c r="J179" s="21"/>
-      <c r="K179" s="21"/>
-      <c r="L179" s="23"/>
+      <c r="J179" s="20"/>
+      <c r="K179" s="20"/>
+      <c r="L179" s="21"/>
       <c r="N179">
         <f>F179*D180</f>
         <v>4.2749999999999995</v>
@@ -13188,9 +12982,9 @@
         <f t="shared" si="20"/>
         <v>-9</v>
       </c>
-      <c r="J180" s="21"/>
-      <c r="K180" s="21"/>
-      <c r="L180" s="23"/>
+      <c r="J180" s="20"/>
+      <c r="K180" s="20"/>
+      <c r="L180" s="21"/>
       <c r="N180">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -13291,15 +13085,15 @@
         <f>G184-H184</f>
         <v>7</v>
       </c>
-      <c r="J184" s="21">
+      <c r="J184" s="20">
         <f>SUM(F184:F198)</f>
         <v>150</v>
       </c>
-      <c r="K184" s="21">
+      <c r="K184" s="20">
         <f>SUM(N185:N198)</f>
         <v>47.798999999999999</v>
       </c>
-      <c r="L184" s="23">
+      <c r="L184" s="21">
         <f>K184/J184</f>
         <v>0.31866</v>
       </c>
@@ -13334,9 +13128,9 @@
         <f t="shared" ref="I185:I198" si="25">G185-H185</f>
         <v>-3</v>
       </c>
-      <c r="J185" s="21"/>
-      <c r="K185" s="21"/>
-      <c r="L185" s="23"/>
+      <c r="J185" s="20"/>
+      <c r="K185" s="20"/>
+      <c r="L185" s="21"/>
       <c r="N185">
         <f>F184*D185</f>
         <v>3.3249999999999997</v>
@@ -13372,9 +13166,9 @@
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
-      <c r="J186" s="21"/>
-      <c r="K186" s="21"/>
-      <c r="L186" s="23"/>
+      <c r="J186" s="20"/>
+      <c r="K186" s="20"/>
+      <c r="L186" s="21"/>
       <c r="N186">
         <f t="shared" ref="N186:N196" si="27">F185*D186</f>
         <v>1.764</v>
@@ -13410,9 +13204,9 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J187" s="21"/>
-      <c r="K187" s="21"/>
-      <c r="L187" s="23"/>
+      <c r="J187" s="20"/>
+      <c r="K187" s="20"/>
+      <c r="L187" s="21"/>
       <c r="N187">
         <f t="shared" si="27"/>
         <v>2.6999999999999997</v>
@@ -13448,9 +13242,9 @@
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
-      <c r="J188" s="21"/>
-      <c r="K188" s="21"/>
-      <c r="L188" s="23"/>
+      <c r="J188" s="20"/>
+      <c r="K188" s="20"/>
+      <c r="L188" s="21"/>
       <c r="N188">
         <f t="shared" si="27"/>
         <v>2.1869999999999998</v>
@@ -13486,9 +13280,9 @@
         <f t="shared" si="25"/>
         <v>5</v>
       </c>
-      <c r="J189" s="21"/>
-      <c r="K189" s="21"/>
-      <c r="L189" s="23"/>
+      <c r="J189" s="20"/>
+      <c r="K189" s="20"/>
+      <c r="L189" s="21"/>
       <c r="N189">
         <f t="shared" si="27"/>
         <v>4.0179999999999998</v>
@@ -13524,9 +13318,9 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J190" s="21"/>
-      <c r="K190" s="21"/>
-      <c r="L190" s="23"/>
+      <c r="J190" s="20"/>
+      <c r="K190" s="20"/>
+      <c r="L190" s="21"/>
       <c r="N190">
         <f t="shared" si="27"/>
         <v>3.4769999999999999</v>
@@ -13562,9 +13356,9 @@
         <f t="shared" si="25"/>
         <v>-1</v>
       </c>
-      <c r="J191" s="21"/>
-      <c r="K191" s="21"/>
-      <c r="L191" s="23"/>
+      <c r="J191" s="20"/>
+      <c r="K191" s="20"/>
+      <c r="L191" s="21"/>
       <c r="N191">
         <f t="shared" si="27"/>
         <v>7.7899999999999991</v>
@@ -13600,9 +13394,9 @@
         <f t="shared" si="25"/>
         <v>-3</v>
       </c>
-      <c r="J192" s="21"/>
-      <c r="K192" s="21"/>
-      <c r="L192" s="23"/>
+      <c r="J192" s="20"/>
+      <c r="K192" s="20"/>
+      <c r="L192" s="21"/>
       <c r="N192">
         <f t="shared" si="27"/>
         <v>6.3</v>
@@ -13638,9 +13432,9 @@
         <f t="shared" si="25"/>
         <v>-1</v>
       </c>
-      <c r="J193" s="21"/>
-      <c r="K193" s="21"/>
-      <c r="L193" s="23"/>
+      <c r="J193" s="20"/>
+      <c r="K193" s="20"/>
+      <c r="L193" s="21"/>
       <c r="N193">
         <f t="shared" si="27"/>
         <v>5.34</v>
@@ -13676,9 +13470,9 @@
         <f t="shared" si="25"/>
         <v>-4</v>
       </c>
-      <c r="J194" s="21"/>
-      <c r="K194" s="21"/>
-      <c r="L194" s="23"/>
+      <c r="J194" s="20"/>
+      <c r="K194" s="20"/>
+      <c r="L194" s="21"/>
       <c r="N194">
         <f t="shared" si="27"/>
         <v>5.0819999999999999</v>
@@ -13714,9 +13508,9 @@
         <f t="shared" si="25"/>
         <v>-6</v>
       </c>
-      <c r="J195" s="21"/>
-      <c r="K195" s="21"/>
-      <c r="L195" s="23"/>
+      <c r="J195" s="20"/>
+      <c r="K195" s="20"/>
+      <c r="L195" s="21"/>
       <c r="N195">
         <f t="shared" si="27"/>
         <v>3.04</v>
@@ -13752,9 +13546,9 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J196" s="21"/>
-      <c r="K196" s="21"/>
-      <c r="L196" s="23"/>
+      <c r="J196" s="20"/>
+      <c r="K196" s="20"/>
+      <c r="L196" s="21"/>
       <c r="N196">
         <f t="shared" si="27"/>
         <v>0.71599999999999997</v>
@@ -13790,9 +13584,9 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="J197" s="21"/>
-      <c r="K197" s="21"/>
-      <c r="L197" s="23"/>
+      <c r="J197" s="20"/>
+      <c r="K197" s="20"/>
+      <c r="L197" s="21"/>
       <c r="N197">
         <f>F196*D197</f>
         <v>1.3720000000000001</v>
@@ -13828,9 +13622,9 @@
         <f t="shared" si="25"/>
         <v>-4</v>
       </c>
-      <c r="J198" s="21"/>
-      <c r="K198" s="21"/>
-      <c r="L198" s="23"/>
+      <c r="J198" s="20"/>
+      <c r="K198" s="20"/>
+      <c r="L198" s="21"/>
       <c r="N198">
         <f>F197*D198</f>
         <v>0.68799999999999994</v>
@@ -13974,7 +13768,7 @@
       <c r="E220" s="1">
         <v>7</v>
       </c>
-      <c r="F220" s="21">
+      <c r="F220" s="20">
         <v>142</v>
       </c>
       <c r="H220" s="1">
@@ -13992,7 +13786,7 @@
       <c r="L220">
         <v>7</v>
       </c>
-      <c r="M220" s="21">
+      <c r="M220" s="20">
         <f>SUM(I220:I234)</f>
         <v>150</v>
       </c>
@@ -14013,7 +13807,7 @@
       <c r="E221" s="1">
         <v>12</v>
       </c>
-      <c r="F221" s="21"/>
+      <c r="F221" s="20"/>
       <c r="H221" s="1">
         <v>2</v>
       </c>
@@ -14029,7 +13823,7 @@
       <c r="L221">
         <v>-3</v>
       </c>
-      <c r="M221" s="21"/>
+      <c r="M221" s="20"/>
     </row>
     <row r="222" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
@@ -14047,7 +13841,7 @@
       <c r="E222" s="1">
         <v>-8</v>
       </c>
-      <c r="F222" s="21"/>
+      <c r="F222" s="20"/>
       <c r="H222" s="1">
         <v>3</v>
       </c>
@@ -14063,7 +13857,7 @@
       <c r="L222">
         <v>5</v>
       </c>
-      <c r="M222" s="21"/>
+      <c r="M222" s="20"/>
     </row>
     <row r="223" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
@@ -14081,7 +13875,7 @@
       <c r="E223" s="1">
         <v>-2</v>
       </c>
-      <c r="F223" s="21"/>
+      <c r="F223" s="20"/>
       <c r="H223" s="1">
         <v>4</v>
       </c>
@@ -14097,7 +13891,7 @@
       <c r="L223">
         <v>0</v>
       </c>
-      <c r="M223" s="21"/>
+      <c r="M223" s="20"/>
     </row>
     <row r="224" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
@@ -14115,7 +13909,7 @@
       <c r="E224" s="1">
         <v>4</v>
       </c>
-      <c r="F224" s="21"/>
+      <c r="F224" s="20"/>
       <c r="H224" s="1">
         <v>5</v>
       </c>
@@ -14131,7 +13925,7 @@
       <c r="L224">
         <v>5</v>
       </c>
-      <c r="M224" s="21"/>
+      <c r="M224" s="20"/>
     </row>
     <row r="225" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
@@ -14149,7 +13943,7 @@
       <c r="E225" s="1">
         <v>-1</v>
       </c>
-      <c r="F225" s="21"/>
+      <c r="F225" s="20"/>
       <c r="H225" s="1">
         <v>6</v>
       </c>
@@ -14165,7 +13959,7 @@
       <c r="L225">
         <v>5</v>
       </c>
-      <c r="M225" s="21"/>
+      <c r="M225" s="20"/>
     </row>
     <row r="226" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
@@ -14183,7 +13977,7 @@
       <c r="E226" s="1">
         <v>-1</v>
       </c>
-      <c r="F226" s="21"/>
+      <c r="F226" s="20"/>
       <c r="H226" s="1">
         <v>7</v>
       </c>
@@ -14199,7 +13993,7 @@
       <c r="L226">
         <v>0</v>
       </c>
-      <c r="M226" s="21"/>
+      <c r="M226" s="20"/>
     </row>
     <row r="227" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
@@ -14217,7 +14011,7 @@
       <c r="E227" s="1">
         <v>-4</v>
       </c>
-      <c r="F227" s="21"/>
+      <c r="F227" s="20"/>
       <c r="H227" s="1">
         <v>8</v>
       </c>
@@ -14233,7 +14027,7 @@
       <c r="L227">
         <v>-1</v>
       </c>
-      <c r="M227" s="21"/>
+      <c r="M227" s="20"/>
     </row>
     <row r="228" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
@@ -14251,7 +14045,7 @@
       <c r="E228" s="1">
         <v>2</v>
       </c>
-      <c r="F228" s="21"/>
+      <c r="F228" s="20"/>
       <c r="H228" s="1">
         <v>9</v>
       </c>
@@ -14267,7 +14061,7 @@
       <c r="L228">
         <v>-3</v>
       </c>
-      <c r="M228" s="21"/>
+      <c r="M228" s="20"/>
     </row>
     <row r="229" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
@@ -14285,7 +14079,7 @@
       <c r="E229" s="1">
         <v>1</v>
       </c>
-      <c r="F229" s="21"/>
+      <c r="F229" s="20"/>
       <c r="H229" s="1">
         <v>10</v>
       </c>
@@ -14301,7 +14095,7 @@
       <c r="L229">
         <v>-1</v>
       </c>
-      <c r="M229" s="21"/>
+      <c r="M229" s="20"/>
     </row>
     <row r="230" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
@@ -14319,7 +14113,7 @@
       <c r="E230" s="1">
         <v>2</v>
       </c>
-      <c r="F230" s="21"/>
+      <c r="F230" s="20"/>
       <c r="H230" s="1">
         <v>11</v>
       </c>
@@ -14335,7 +14129,7 @@
       <c r="L230">
         <v>-4</v>
       </c>
-      <c r="M230" s="21"/>
+      <c r="M230" s="20"/>
     </row>
     <row r="231" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
@@ -14353,7 +14147,7 @@
       <c r="E231" s="1">
         <v>-4</v>
       </c>
-      <c r="F231" s="21"/>
+      <c r="F231" s="20"/>
       <c r="H231" s="1">
         <v>12</v>
       </c>
@@ -14369,7 +14163,7 @@
       <c r="L231">
         <v>-6</v>
       </c>
-      <c r="M231" s="21"/>
+      <c r="M231" s="20"/>
     </row>
     <row r="232" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
@@ -14387,7 +14181,7 @@
       <c r="E232" s="1">
         <v>-3</v>
       </c>
-      <c r="F232" s="21"/>
+      <c r="F232" s="20"/>
       <c r="H232" s="1">
         <v>13</v>
       </c>
@@ -14403,7 +14197,7 @@
       <c r="L232">
         <v>0</v>
       </c>
-      <c r="M232" s="21"/>
+      <c r="M232" s="20"/>
     </row>
     <row r="233" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
@@ -14421,7 +14215,7 @@
       <c r="E233" s="1">
         <v>4</v>
       </c>
-      <c r="F233" s="21"/>
+      <c r="F233" s="20"/>
       <c r="H233" s="1">
         <v>14</v>
       </c>
@@ -14437,7 +14231,7 @@
       <c r="L233">
         <v>0</v>
       </c>
-      <c r="M233" s="21"/>
+      <c r="M233" s="20"/>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
@@ -14455,7 +14249,7 @@
       <c r="E234" s="1">
         <v>-9</v>
       </c>
-      <c r="F234" s="21"/>
+      <c r="F234" s="20"/>
       <c r="H234" s="1">
         <v>15</v>
       </c>
@@ -14471,10 +14265,16 @@
       <c r="L234">
         <v>-4</v>
       </c>
-      <c r="M234" s="21"/>
+      <c r="M234" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F64:I64"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
     <mergeCell ref="F220:F234"/>
     <mergeCell ref="M220:M234"/>
     <mergeCell ref="J166:J180"/>
@@ -14483,12 +14283,6 @@
     <mergeCell ref="K184:K198"/>
     <mergeCell ref="L166:L180"/>
     <mergeCell ref="L184:L198"/>
-    <mergeCell ref="F64:I64"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
